--- a/plan_renovation_solution.xlsx
+++ b/plan_renovation_solution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youss\Desktop\Projet ST7\sia_efficacity_projet_st7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024FAB5E-E08B-439E-8FF1-AFE7190D9929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4B85AC-F14B-4B6B-A28F-CF374B28D179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="transitions" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="288">
   <si>
     <t>building</t>
   </si>
@@ -64,754 +64,739 @@
     <t>roof_isolation</t>
   </si>
   <si>
-    <t>abri_bouliste_simulation_7</t>
+    <t>abri_bouliste_simulation_4</t>
+  </si>
+  <si>
+    <t>floor_isolation</t>
+  </si>
+  <si>
+    <t>abri_bouliste_simulation_11</t>
   </si>
   <si>
     <t>window_replacement_DG</t>
   </si>
   <si>
-    <t>abri_bouliste_simulation_11</t>
-  </si>
-  <si>
-    <t>floor_isolation</t>
-  </si>
-  <si>
     <t>accueil_de_loisirs_maternel_la_varenne</t>
   </si>
   <si>
-    <t>accueil_de_loisirs_maternel_la_varenne_simulation_1</t>
+    <t>accueil_de_loisirs_maternel_la_varenne_simulation_3</t>
   </si>
   <si>
     <t>accueil_de_loisirs_maternel_la_varenne_simulation_14</t>
   </si>
   <si>
+    <t>indoor_wall_isolation, window_replacement_TG, floor_isolation</t>
+  </si>
+  <si>
+    <t>association_31_rue_gambetta</t>
+  </si>
+  <si>
+    <t>association_31_rue_gambetta_simulation_1</t>
+  </si>
+  <si>
+    <t>association_31_rue_gambetta_simulation_6</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, roof_isolation</t>
+  </si>
+  <si>
+    <t>ateliers_municipaux_(ctm)</t>
+  </si>
+  <si>
+    <t>ateliers_municipaux_(ctm)_simulation_8</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, roof_isolation, VMC_installation, system_installation</t>
+  </si>
+  <si>
+    <t>ateliers_municipaux_(ctm)_simulation_9</t>
+  </si>
+  <si>
+    <t>base_de_canoe_kayak</t>
+  </si>
+  <si>
+    <t>base_de_canoe_kayak_simulation_3</t>
+  </si>
+  <si>
+    <t>indoor_wall_isolation, floor_isolation</t>
+  </si>
+  <si>
+    <t>base_de_canoe_kayak_simulation_12</t>
+  </si>
+  <si>
+    <t>bureaux_21_rue_des_sports</t>
+  </si>
+  <si>
+    <t>bureaux_21_rue_des_sports_simulation_1</t>
+  </si>
+  <si>
+    <t>bureaux_21_rue_des_sports_simulation_14</t>
+  </si>
+  <si>
+    <t>cdj_du_champy</t>
+  </si>
+  <si>
+    <t>cdj_du_champy_simulation_12</t>
+  </si>
+  <si>
+    <t>floor_isolation, VMC_installation</t>
+  </si>
+  <si>
+    <t>cdj_du_champy_simulation_8</t>
+  </si>
+  <si>
+    <t>indoor_wall_isolation, roof_isolation</t>
+  </si>
+  <si>
+    <t>cdj_du_pave_neuf</t>
+  </si>
+  <si>
+    <t>cdj_du_pave_neuf_simulation_1</t>
+  </si>
+  <si>
+    <t>cdj_du_pave_neuf_simulation_3</t>
+  </si>
+  <si>
+    <t>cdj_du_pave_neuf_simulation_11</t>
+  </si>
+  <si>
+    <t>centre_aquatique_les_nymphéas</t>
+  </si>
+  <si>
+    <t>centre_aquatique_les_nymphéas_simulation_1</t>
+  </si>
+  <si>
+    <t>centre_horticole</t>
+  </si>
+  <si>
+    <t>centre_horticole_simulation_3</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation</t>
+  </si>
+  <si>
+    <t>centre_horticole_simulation_7</t>
+  </si>
+  <si>
+    <t>centre_horticole_simulation_15</t>
+  </si>
+  <si>
+    <t>window_replacement_TG</t>
+  </si>
+  <si>
+    <t>cimetiere_nouveau</t>
+  </si>
+  <si>
+    <t>cimetiere_nouveau_simulation_1</t>
+  </si>
+  <si>
+    <t>cimetiere_nouveau_simulation_5</t>
+  </si>
+  <si>
+    <t>VMC_installation</t>
+  </si>
+  <si>
+    <t>cimetiere_nouveau_simulation_11</t>
+  </si>
+  <si>
+    <t>floor_isolation, roof_isolation</t>
+  </si>
+  <si>
+    <t>cinéma_le_bijou</t>
+  </si>
+  <si>
+    <t>cinéma_le_bijou_simulation_6</t>
+  </si>
+  <si>
+    <t>floor_isolation, system_installation</t>
+  </si>
+  <si>
+    <t>cinéma_le_bijou_simulation_7</t>
+  </si>
+  <si>
+    <t>club_ricardo_bofil</t>
+  </si>
+  <si>
+    <t>club_ricardo_bofil_simulation_2</t>
+  </si>
+  <si>
+    <t>conservatoire_maurice_bacquet</t>
+  </si>
+  <si>
+    <t>conservatoire_maurice_bacquet_simulation 5</t>
+  </si>
+  <si>
+    <t>system_installation</t>
+  </si>
+  <si>
+    <t>conservatoire_maurice_bacquet_simulation 8</t>
+  </si>
+  <si>
+    <t>conservatoire_maurice_bacquet_simulation 10</t>
+  </si>
+  <si>
+    <t>creche_multi_accueil_des_farfadets</t>
+  </si>
+  <si>
+    <t>creche_multi_accueil_des_farfadets_simulation_1</t>
+  </si>
+  <si>
+    <t>creche_multi_accueil_des_farfadets_simulation_2</t>
+  </si>
+  <si>
+    <t>crèche_et_halte_du_marnois</t>
+  </si>
+  <si>
+    <t>crèche_et_halte_du_marnois_simulation_1</t>
+  </si>
+  <si>
+    <t>crèche_et_halte_du_marnois_simulation_6</t>
+  </si>
+  <si>
+    <t>crèche_et_halte_du_marnois_simulation_10</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, VMC_installation</t>
+  </si>
+  <si>
+    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles</t>
+  </si>
+  <si>
+    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles_simulation_4</t>
+  </si>
+  <si>
+    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles_simulation_3</t>
+  </si>
+  <si>
+    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles_simulation_6</t>
+  </si>
+  <si>
+    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles_simulation_7</t>
+  </si>
+  <si>
+    <t>crèche_petit_prince</t>
+  </si>
+  <si>
+    <t>crèche_petit_prince_simulation_3</t>
+  </si>
+  <si>
+    <t>crèche_petit_prince_simulation_7</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, window_replacement_TG</t>
+  </si>
+  <si>
+    <t>crèche_robert_debré</t>
+  </si>
+  <si>
+    <t>crèche_robert_debré_simulation_8</t>
+  </si>
+  <si>
+    <t>crèche_robert_debré_simulation_9</t>
+  </si>
+  <si>
+    <t>indoor_wall_isolation, roof_isolation, VMC_installation</t>
+  </si>
+  <si>
+    <t>crèche_robert_debré_simulation_10</t>
+  </si>
+  <si>
+    <t>déchèterie_municipale</t>
+  </si>
+  <si>
+    <t>déchèterie_municipale_simulation_1</t>
+  </si>
+  <si>
+    <t>déchèterie_municipale_simulation_4</t>
+  </si>
+  <si>
+    <t>déchèterie_municipale_simulation_11</t>
+  </si>
+  <si>
+    <t>emaus_1_et__2</t>
+  </si>
+  <si>
+    <t>emaus_1_et__2_simulation_1</t>
+  </si>
+  <si>
+    <t>emaus_1_et__2_simulation_15</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, floor_isolation, roof_isolation</t>
+  </si>
+  <si>
+    <t>espace_michel_simon</t>
+  </si>
+  <si>
+    <t>espace_michel_simon_simulation 4</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_des_hauts_bâtons</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_des_hauts_bâtons_simulation_7</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, roof_isolation, system_installation</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_des_hauts_bâtons_simulation_9</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_les_coteaux</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_les_coteaux_simulation_13</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, roof_isolation</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_les_richardets</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_les_richardets_simulation_1</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, floor_isolation, roof_isolation, VMC_installation, system_installation</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_paul_serelle</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_paul_serelle_simulation_1</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, floor_isolation, roof_isolation</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_robert_desnos</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_robert_desnos_simulation_7</t>
+  </si>
+  <si>
+    <t>indoor_wall_isolation, roof_isolation, system_installation</t>
+  </si>
+  <si>
+    <t>groupe_scolaire_robert_desnos_simulation_10</t>
+  </si>
+  <si>
+    <t>gs_alex_dumas</t>
+  </si>
+  <si>
+    <t>gs_alex_dumas_simulation 3</t>
+  </si>
+  <si>
+    <t>gs_alex_dumas_simulation 10</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, window_replacement_TG, VMC_installation</t>
+  </si>
+  <si>
+    <t>gs_celestin_freinet</t>
+  </si>
+  <si>
+    <t>gs_celestin_freinet_simulation 2</t>
+  </si>
+  <si>
+    <t>gs_celestin_freinet_simulation 10</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, roof_isolation, VMC_installation</t>
+  </si>
+  <si>
+    <t>gs_clos_arche</t>
+  </si>
+  <si>
+    <t>gs_clos_arche_simulation 2</t>
+  </si>
+  <si>
+    <t>gs_clos_arche_simulation 10</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, floor_isolation, VMC_installation, system_installation</t>
+  </si>
+  <si>
+    <t>gs_clos_dambert</t>
+  </si>
+  <si>
+    <t>gs_clos_dambert_simulation 6</t>
+  </si>
+  <si>
+    <t>indoor_wall_isolation, VMC_installation</t>
+  </si>
+  <si>
+    <t>gs_clos_dambert_simulation 10</t>
+  </si>
+  <si>
+    <t>gs_george_brassens</t>
+  </si>
+  <si>
+    <t>gs_george_brassens_simulation 1</t>
+  </si>
+  <si>
+    <t>gs_george_brassens_simulation 8</t>
+  </si>
+  <si>
     <t>window_replacement_TG, floor_isolation, roof_isolation</t>
   </si>
   <si>
-    <t>association_31_rue_gambetta</t>
-  </si>
-  <si>
-    <t>association_31_rue_gambetta_simulation_1</t>
-  </si>
-  <si>
-    <t>association_31_rue_gambetta_simulation_6</t>
-  </si>
-  <si>
-    <t>window_replacement_DG, roof_isolation</t>
-  </si>
-  <si>
-    <t>ateliers_municipaux_(ctm)</t>
-  </si>
-  <si>
-    <t>ateliers_municipaux_(ctm)_simulation_6</t>
-  </si>
-  <si>
-    <t>system_installation</t>
-  </si>
-  <si>
-    <t>ateliers_municipaux_(ctm)_simulation_8</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, roof_isolation, VMC_installation</t>
-  </si>
-  <si>
-    <t>ateliers_municipaux_(ctm)_simulation_9</t>
-  </si>
-  <si>
-    <t>base_de_canoe_kayak</t>
-  </si>
-  <si>
-    <t>base_de_canoe_kayak_simulation_3</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, floor_isolation</t>
-  </si>
-  <si>
-    <t>base_de_canoe_kayak_simulation_12</t>
-  </si>
-  <si>
-    <t>bureaux_21_rue_des_sports</t>
-  </si>
-  <si>
-    <t>bureaux_21_rue_des_sports_simulation_3</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, roof_isolation</t>
-  </si>
-  <si>
-    <t>bureaux_21_rue_des_sports_simulation_14</t>
-  </si>
-  <si>
-    <t>cdj_du_champy</t>
-  </si>
-  <si>
-    <t>cdj_du_champy_simulation_9</t>
-  </si>
-  <si>
-    <t>VMC_installation</t>
-  </si>
-  <si>
-    <t>cdj_du_champy_simulation_4</t>
-  </si>
-  <si>
-    <t>cdj_du_champy_simulation_8</t>
-  </si>
-  <si>
-    <t>cdj_du_pave_neuf</t>
-  </si>
-  <si>
-    <t>cdj_du_pave_neuf_simulation_1</t>
-  </si>
-  <si>
-    <t>cdj_du_pave_neuf_simulation_3</t>
-  </si>
-  <si>
-    <t>cdj_du_pave_neuf_simulation_11</t>
-  </si>
-  <si>
-    <t>floor_isolation, VMC_installation</t>
-  </si>
-  <si>
-    <t>centre_aquatique_les_nymphéas</t>
-  </si>
-  <si>
-    <t>centre_aquatique_les_nymphéas_simulation_1</t>
-  </si>
-  <si>
-    <t>centre_horticole</t>
-  </si>
-  <si>
-    <t>centre_horticole_simulation_3</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation</t>
-  </si>
-  <si>
-    <t>centre_horticole_simulation_15</t>
+    <t>gs_joliot_curie</t>
+  </si>
+  <si>
+    <t>gs_joliot_curie_simulation 8</t>
+  </si>
+  <si>
+    <t>gs_joliot_curie_simulation 9</t>
+  </si>
+  <si>
+    <t>gs_jules_ferry</t>
+  </si>
+  <si>
+    <t>gs_jules_ferry_simulation 5</t>
+  </si>
+  <si>
+    <t>gs_jules_ferry_simulation 8</t>
+  </si>
+  <si>
+    <t>gs_jules_ferry_simulation 10</t>
+  </si>
+  <si>
+    <t>gs_jules_verne</t>
+  </si>
+  <si>
+    <t>gs_jules_verne_simulation 1</t>
+  </si>
+  <si>
+    <t>gs_jules_verne_simulation 8</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, floor_isolation</t>
+  </si>
+  <si>
+    <t>gs_jules_verne_simulation 10</t>
+  </si>
+  <si>
+    <t>gs_la_varenne</t>
+  </si>
+  <si>
+    <t>gs_la_varenne_simulation 5</t>
+  </si>
+  <si>
+    <t>gs_la_varenne_simulation 7</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, floor_isolation</t>
+  </si>
+  <si>
+    <t>gs_la_varenne_simulation 10</t>
+  </si>
+  <si>
+    <t>gs_les_abeilles</t>
+  </si>
+  <si>
+    <t>gs_les_abeilles_simulation 2</t>
+  </si>
+  <si>
+    <t>gs_les_abeilles_simulation 10</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, roof_isolation, VMC_installation, system_installation</t>
+  </si>
+  <si>
+    <t>gs_les_charmilles</t>
+  </si>
+  <si>
+    <t>gs_les_charmilles_simulation 1</t>
+  </si>
+  <si>
+    <t>gs_les_charmilles_simulation 10</t>
+  </si>
+  <si>
+    <t>gs_les_noyers</t>
+  </si>
+  <si>
+    <t>gs_les_noyers_simulation 2</t>
+  </si>
+  <si>
+    <t>gs_les_noyers_simulation 8</t>
+  </si>
+  <si>
+    <t>roof_isolation, system_installation</t>
+  </si>
+  <si>
+    <t>gs_les_noyers_simulation 10</t>
+  </si>
+  <si>
+    <t>gs_les_yvris</t>
+  </si>
+  <si>
+    <t>gs_les_yvris_simulation 1</t>
+  </si>
+  <si>
+    <t>gs_les_yvris_simulation 10</t>
+  </si>
+  <si>
+    <t>window_replacement_TG, VMC_installation</t>
+  </si>
+  <si>
+    <t>gs_van_gogh</t>
+  </si>
+  <si>
+    <t>gs_van_gogh_simulation 1</t>
+  </si>
+  <si>
+    <t>gs_van_gogh_simulation 10</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, roof_isolation, system_installation</t>
+  </si>
+  <si>
+    <t>gymnase_champy</t>
+  </si>
+  <si>
+    <t>gymnase_champy_simulation 8</t>
+  </si>
+  <si>
+    <t>VMC_installation, system_installation</t>
+  </si>
+  <si>
+    <t>gymnase_champy_simulation 10</t>
+  </si>
+  <si>
+    <t>gymnase_de_la_butte_verte</t>
+  </si>
+  <si>
+    <t>gymnase_de_la_butte_verte_simulation_3</t>
+  </si>
+  <si>
+    <t>gymnase_de_la_butte_verte_simulation_8</t>
+  </si>
+  <si>
+    <t>gymnase_du_clos_de_l'arche</t>
+  </si>
+  <si>
+    <t>gymnase_du_clos_de_l'arche_simulation_2</t>
+  </si>
+  <si>
+    <t>gymnase_la_varenne</t>
+  </si>
+  <si>
+    <t>gymnase_la_varenne_simulation 5</t>
+  </si>
+  <si>
+    <t>gymnase_la_varenne_simulation 10</t>
+  </si>
+  <si>
+    <t>window_replacement_DG, system_installation</t>
+  </si>
+  <si>
+    <t>gymnase_les_coteaux</t>
+  </si>
+  <si>
+    <t>gymnase_les_coteaux_simulation_1</t>
+  </si>
+  <si>
+    <t>gymnase_les_coteaux_simulation_9</t>
+  </si>
+  <si>
+    <t>gymnase_les_yvris</t>
+  </si>
+  <si>
+    <t>gymnase_les_yvris_simulation_1</t>
+  </si>
+  <si>
+    <t>gymnase_les_yvris_simulation_7</t>
+  </si>
+  <si>
+    <t>gymnase_les_yvris_simulation_10</t>
+  </si>
+  <si>
+    <t>gymnase_louison_bobet</t>
+  </si>
+  <si>
+    <t>gymnase_louison_bobet_simulation 3</t>
+  </si>
+  <si>
+    <t>gymnase_louison_bobet_simulation 10</t>
+  </si>
+  <si>
+    <t>hangar_bleu</t>
+  </si>
+  <si>
+    <t>hangar_bleu_simulation_2</t>
+  </si>
+  <si>
+    <t>hangar_bleu_simulation_3</t>
+  </si>
+  <si>
+    <t>hangar_bleu_simulation_9</t>
+  </si>
+  <si>
+    <t>local_associatif_pablo_picasso</t>
+  </si>
+  <si>
+    <t>local_associatif_pablo_picasso_simulation_1</t>
+  </si>
+  <si>
+    <t>local_associatif_pablo_picasso_simulation_7</t>
+  </si>
+  <si>
+    <t>maison_de_la_jeunesse</t>
+  </si>
+  <si>
+    <t>maison_de_la_jeunesse_simulation_1</t>
+  </si>
+  <si>
+    <t>maison_de_la_jeunesse_simulation_9</t>
+  </si>
+  <si>
+    <t>floor_isolation, roof_isolation, VMC_installation</t>
+  </si>
+  <si>
+    <t>maison_des_services_publics_-_pimms</t>
+  </si>
+  <si>
+    <t>maison_des_services_publics_-_pimms_simulation_1</t>
+  </si>
+  <si>
+    <t>maison_des_services_publics_-_pimms_simulation_2</t>
+  </si>
+  <si>
+    <t>maison_des_services_publics_-_pimms_simulation_13</t>
+  </si>
+  <si>
+    <t>maison_des_syndicats</t>
+  </si>
+  <si>
+    <t>maison_des_syndicats_simulation_1</t>
+  </si>
+  <si>
+    <t>maison_des_syndicats_simulation_11</t>
   </si>
   <si>
     <t>window_replacement_TG, roof_isolation</t>
   </si>
   <si>
-    <t>cimetiere_nouveau</t>
-  </si>
-  <si>
-    <t>cimetiere_nouveau_simulation_6</t>
-  </si>
-  <si>
-    <t>cimetiere_nouveau_simulation_11</t>
+    <t>maison_medicale_du_champy</t>
+  </si>
+  <si>
+    <t>maison_medicale_du_champy_simulation_8</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, floor_isolation, VMC_installation</t>
+  </si>
+  <si>
+    <t>maison_medicale_du_champy_simulation_14</t>
+  </si>
+  <si>
+    <t>medecine_du_travail</t>
+  </si>
+  <si>
+    <t>medecine_du_travail_simulation_3</t>
+  </si>
+  <si>
+    <t>medecine_du_travail_simulation_8</t>
+  </si>
+  <si>
+    <t>mille_club_des_yvris</t>
+  </si>
+  <si>
+    <t>mille_club_des_yvris_simulation_8</t>
+  </si>
+  <si>
+    <t>mille_club_des_yvris_simulation_4</t>
+  </si>
+  <si>
+    <t>mille_club_des_yvris_simulation_7</t>
+  </si>
+  <si>
+    <t>mpt_des_coteaux</t>
+  </si>
+  <si>
+    <t>mpt_des_coteaux_simulation_8</t>
+  </si>
+  <si>
+    <t>mpt_des_coteaux_simulation_13</t>
+  </si>
+  <si>
+    <t>mpt_du_champy</t>
+  </si>
+  <si>
+    <t>mpt_du_champy_simulation_4</t>
+  </si>
+  <si>
+    <t>mpt_du_champy_simulation_10</t>
+  </si>
+  <si>
+    <t>indoor_wall_isolation, window_replacement_TG, VMC_installation</t>
+  </si>
+  <si>
+    <t>mpt_jardin_des_sources_-_annexe_maison_pour_tous</t>
+  </si>
+  <si>
+    <t>mpt_jardin_des_sources_-_annexe_maison_pour_tous_simulation_5</t>
+  </si>
+  <si>
+    <t>exterior_wall_isolation, window_replacement_TG, floor_isolation</t>
+  </si>
+  <si>
+    <t>mpt_la_varenne</t>
+  </si>
+  <si>
+    <t>mpt_la_varenne_simulation 6</t>
+  </si>
+  <si>
+    <t>mpt_la_varenne_simulation 10</t>
+  </si>
+  <si>
+    <t>indoor_wall_isolation, window_replacement_TG, roof_isolation, system_installation</t>
+  </si>
+  <si>
+    <t>mpt_les_richardets</t>
+  </si>
+  <si>
+    <t>mpt_les_richardets_simulation_5</t>
+  </si>
+  <si>
+    <t>mpt_les_richardets_simulation_10</t>
+  </si>
+  <si>
+    <t>indoor_wall_isolation, window_replacement_DG, roof_isolation</t>
+  </si>
+  <si>
+    <t>mpt_marcel_bou</t>
+  </si>
+  <si>
+    <t>mpt_marcel_bou_simulation 1</t>
+  </si>
+  <si>
+    <t>mpt_marcel_bou_simulation 9</t>
+  </si>
+  <si>
+    <t>floor_isolation, roof_isolation, system_installation</t>
+  </si>
+  <si>
+    <t>mpt_marcel_bou_simulation 10</t>
+  </si>
+  <si>
+    <t>multi_accueil_jean_piaget</t>
+  </si>
+  <si>
+    <t>multi_accueil_jean_piaget_simulation_6</t>
   </si>
   <si>
     <t>indoor_wall_isolation, floor_isolation, VMC_installation</t>
   </si>
   <si>
-    <t>cinéma_le_bijou</t>
-  </si>
-  <si>
-    <t>cinéma_le_bijou_simulation_6</t>
-  </si>
-  <si>
-    <t>floor_isolation, system_installation</t>
-  </si>
-  <si>
-    <t>cinéma_le_bijou_simulation_7</t>
-  </si>
-  <si>
-    <t>window_replacement_TG</t>
-  </si>
-  <si>
-    <t>club_ricardo_bofil</t>
-  </si>
-  <si>
-    <t>club_ricardo_bofil_simulation_1</t>
-  </si>
-  <si>
-    <t>club_ricardo_bofil_simulation_2</t>
-  </si>
-  <si>
-    <t>conservatoire_maurice_bacquet</t>
-  </si>
-  <si>
-    <t>conservatoire_maurice_bacquet_simulation 5</t>
-  </si>
-  <si>
-    <t>conservatoire_maurice_bacquet_simulation 8</t>
-  </si>
-  <si>
-    <t>conservatoire_maurice_bacquet_simulation 10</t>
-  </si>
-  <si>
-    <t>creche_multi_accueil_des_farfadets</t>
-  </si>
-  <si>
-    <t>creche_multi_accueil_des_farfadets_simulation_3</t>
-  </si>
-  <si>
-    <t>creche_multi_accueil_des_farfadets_simulation_2</t>
-  </si>
-  <si>
-    <t>crèche_et_halte_du_marnois</t>
-  </si>
-  <si>
-    <t>crèche_et_halte_du_marnois_simulation_1</t>
-  </si>
-  <si>
-    <t>crèche_et_halte_du_marnois_simulation_6</t>
-  </si>
-  <si>
-    <t>crèche_et_halte_du_marnois_simulation_10</t>
-  </si>
-  <si>
-    <t>window_replacement_DG, VMC_installation</t>
-  </si>
-  <si>
-    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles</t>
-  </si>
-  <si>
-    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles_simulation_4</t>
-  </si>
-  <si>
-    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles_simulation_2</t>
-  </si>
-  <si>
-    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles_simulation_6</t>
-  </si>
-  <si>
-    <t>crèche_familiale_du_champy_-_relais_des_assistances_maternelles_simulation_7</t>
-  </si>
-  <si>
-    <t>crèche_petit_prince</t>
-  </si>
-  <si>
-    <t>crèche_petit_prince_simulation_3</t>
-  </si>
-  <si>
-    <t>crèche_petit_prince_simulation_6</t>
-  </si>
-  <si>
-    <t>crèche_petit_prince_simulation_7</t>
-  </si>
-  <si>
-    <t>crèche_robert_debré</t>
-  </si>
-  <si>
-    <t>crèche_robert_debré_simulation_8</t>
-  </si>
-  <si>
-    <t>crèche_robert_debré_simulation_10</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, window_replacement_DG, roof_isolation, VMC_installation</t>
-  </si>
-  <si>
-    <t>déchèterie_municipale</t>
-  </si>
-  <si>
-    <t>déchèterie_municipale_simulation_4</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, floor_isolation, roof_isolation</t>
-  </si>
-  <si>
-    <t>déchèterie_municipale_simulation_11</t>
-  </si>
-  <si>
-    <t>emaus_1_et__2</t>
-  </si>
-  <si>
-    <t>emaus_1_et__2_simulation_1</t>
-  </si>
-  <si>
-    <t>emaus_1_et__2_simulation_8</t>
-  </si>
-  <si>
-    <t>emaus_1_et__2_simulation_15</t>
-  </si>
-  <si>
-    <t>floor_isolation, roof_isolation</t>
-  </si>
-  <si>
-    <t>espace_michel_simon</t>
-  </si>
-  <si>
-    <t>espace_michel_simon_simulation 4</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_des_hauts_bâtons</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_des_hauts_bâtons_simulation_7</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, roof_isolation, system_installation</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_des_hauts_bâtons_simulation_8</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_des_hauts_bâtons_simulation_9</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_les_coteaux</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_les_coteaux_simulation_13</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, roof_isolation</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_les_richardets</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_les_richardets_simulation_1</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, floor_isolation, roof_isolation, VMC_installation, system_installation</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_paul_serelle</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_paul_serelle_simulation_1</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, floor_isolation, roof_isolation</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_robert_desnos</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_robert_desnos_simulation_7</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, roof_isolation, system_installation</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_robert_desnos_simulation_9</t>
-  </si>
-  <si>
-    <t>groupe_scolaire_robert_desnos_simulation_10</t>
-  </si>
-  <si>
-    <t>gs_alex_dumas</t>
-  </si>
-  <si>
-    <t>gs_alex_dumas_simulation 3</t>
-  </si>
-  <si>
-    <t>gs_alex_dumas_simulation 10</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, window_replacement_TG, VMC_installation</t>
-  </si>
-  <si>
-    <t>gs_celestin_freinet</t>
-  </si>
-  <si>
-    <t>gs_celestin_freinet_simulation 2</t>
-  </si>
-  <si>
-    <t>gs_celestin_freinet_simulation 6</t>
-  </si>
-  <si>
-    <t>gs_celestin_freinet_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_clos_arche</t>
-  </si>
-  <si>
-    <t>gs_clos_arche_simulation 2</t>
-  </si>
-  <si>
-    <t>gs_clos_arche_simulation 7</t>
-  </si>
-  <si>
-    <t>window_replacement_DG, system_installation</t>
-  </si>
-  <si>
-    <t>gs_clos_arche_simulation 8</t>
-  </si>
-  <si>
-    <t>gs_clos_arche_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_clos_dambert</t>
-  </si>
-  <si>
-    <t>gs_clos_dambert_simulation 6</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, VMC_installation</t>
-  </si>
-  <si>
-    <t>gs_clos_dambert_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_george_brassens</t>
-  </si>
-  <si>
-    <t>gs_george_brassens_simulation 1</t>
-  </si>
-  <si>
-    <t>gs_george_brassens_simulation 8</t>
-  </si>
-  <si>
-    <t>gs_joliot_curie</t>
-  </si>
-  <si>
-    <t>gs_joliot_curie_simulation 8</t>
-  </si>
-  <si>
-    <t>gs_joliot_curie_simulation 9</t>
-  </si>
-  <si>
-    <t>gs_jules_ferry</t>
-  </si>
-  <si>
-    <t>gs_jules_ferry_simulation 4</t>
-  </si>
-  <si>
-    <t>gs_jules_ferry_simulation 7</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, window_replacement_TG</t>
-  </si>
-  <si>
-    <t>gs_jules_ferry_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_jules_verne</t>
-  </si>
-  <si>
-    <t>gs_jules_verne_simulation 1</t>
-  </si>
-  <si>
-    <t>gs_jules_verne_simulation 9</t>
-  </si>
-  <si>
-    <t>gs_jules_verne_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_la_varenne</t>
-  </si>
-  <si>
-    <t>gs_la_varenne_simulation 7</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, floor_isolation, system_installation</t>
-  </si>
-  <si>
-    <t>gs_la_varenne_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_les_abeilles</t>
-  </si>
-  <si>
-    <t>gs_les_abeilles_simulation 2</t>
-  </si>
-  <si>
-    <t>gs_les_abeilles_simulation 8</t>
-  </si>
-  <si>
-    <t>roof_isolation, system_installation</t>
-  </si>
-  <si>
-    <t>gs_les_abeilles_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_les_charmilles</t>
-  </si>
-  <si>
-    <t>gs_les_charmilles_simulation 1</t>
-  </si>
-  <si>
-    <t>gs_les_charmilles_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_les_noyers</t>
-  </si>
-  <si>
-    <t>gs_les_noyers_simulation 2</t>
-  </si>
-  <si>
-    <t>gs_les_noyers_simulation 8</t>
-  </si>
-  <si>
-    <t>gs_les_noyers_simulation 10</t>
-  </si>
-  <si>
-    <t>gs_les_yvris</t>
-  </si>
-  <si>
-    <t>gs_les_yvris_simulation 1</t>
-  </si>
-  <si>
-    <t>gs_les_yvris_simulation 10</t>
-  </si>
-  <si>
-    <t>window_replacement_TG, VMC_installation</t>
-  </si>
-  <si>
-    <t>gs_van_gogh</t>
-  </si>
-  <si>
-    <t>gs_van_gogh_simulation 1</t>
-  </si>
-  <si>
-    <t>gs_van_gogh_simulation 10</t>
-  </si>
-  <si>
-    <t>window_replacement_DG, roof_isolation, system_installation</t>
-  </si>
-  <si>
-    <t>gymnase_champy</t>
-  </si>
-  <si>
-    <t>gymnase_champy_simulation 8</t>
-  </si>
-  <si>
-    <t>VMC_installation, system_installation</t>
-  </si>
-  <si>
-    <t>gymnase_champy_simulation 9</t>
-  </si>
-  <si>
-    <t>gymnase_champy_simulation 10</t>
-  </si>
-  <si>
-    <t>gymnase_de_la_butte_verte</t>
-  </si>
-  <si>
-    <t>gymnase_de_la_butte_verte_simulation_3</t>
-  </si>
-  <si>
-    <t>gymnase_de_la_butte_verte_simulation_5</t>
-  </si>
-  <si>
-    <t>gymnase_de_la_butte_verte_simulation_8</t>
-  </si>
-  <si>
-    <t>gymnase_du_clos_de_l'arche</t>
-  </si>
-  <si>
-    <t>gymnase_du_clos_de_l'arche_simulation_2</t>
-  </si>
-  <si>
-    <t>gymnase_la_varenne</t>
-  </si>
-  <si>
-    <t>gymnase_la_varenne_simulation 5</t>
-  </si>
-  <si>
-    <t>gymnase_la_varenne_simulation 9</t>
-  </si>
-  <si>
-    <t>gymnase_la_varenne_simulation 10</t>
-  </si>
-  <si>
-    <t>gymnase_les_coteaux</t>
-  </si>
-  <si>
-    <t>gymnase_les_coteaux_simulation_1</t>
-  </si>
-  <si>
-    <t>gymnase_les_coteaux_simulation_6</t>
-  </si>
-  <si>
-    <t>gymnase_les_coteaux_simulation_9</t>
-  </si>
-  <si>
-    <t>gymnase_les_yvris</t>
-  </si>
-  <si>
-    <t>gymnase_les_yvris_simulation_1</t>
-  </si>
-  <si>
-    <t>gymnase_les_yvris_simulation_10</t>
-  </si>
-  <si>
-    <t>roof_isolation, VMC_installation, system_installation</t>
-  </si>
-  <si>
-    <t>gymnase_louison_bobet</t>
-  </si>
-  <si>
-    <t>gymnase_louison_bobet_simulation 3</t>
-  </si>
-  <si>
-    <t>gymnase_louison_bobet_simulation 10</t>
-  </si>
-  <si>
-    <t>hangar_bleu</t>
-  </si>
-  <si>
-    <t>hangar_bleu_simulation_2</t>
-  </si>
-  <si>
-    <t>hangar_bleu_simulation_3</t>
-  </si>
-  <si>
-    <t>hangar_bleu_simulation_9</t>
-  </si>
-  <si>
-    <t>local_associatif_pablo_picasso</t>
-  </si>
-  <si>
-    <t>local_associatif_pablo_picasso_simulation_1</t>
-  </si>
-  <si>
-    <t>local_associatif_pablo_picasso_simulation_7</t>
-  </si>
-  <si>
-    <t>window_replacement_DG, floor_isolation</t>
-  </si>
-  <si>
-    <t>maison_de_la_jeunesse</t>
-  </si>
-  <si>
-    <t>maison_de_la_jeunesse_simulation_1</t>
-  </si>
-  <si>
-    <t>maison_de_la_jeunesse_simulation_8</t>
-  </si>
-  <si>
-    <t>maison_de_la_jeunesse_simulation_9</t>
-  </si>
-  <si>
-    <t>maison_des_services_publics_-_pimms</t>
-  </si>
-  <si>
-    <t>maison_des_services_publics_-_pimms_simulation_1</t>
-  </si>
-  <si>
-    <t>maison_des_services_publics_-_pimms_simulation_13</t>
-  </si>
-  <si>
-    <t>window_replacement_DG, floor_isolation, VMC_installation</t>
-  </si>
-  <si>
-    <t>maison_des_syndicats</t>
-  </si>
-  <si>
-    <t>maison_des_syndicats_simulation_13</t>
-  </si>
-  <si>
-    <t>maison_des_syndicats_simulation_11</t>
-  </si>
-  <si>
-    <t>maison_medicale_du_champy</t>
-  </si>
-  <si>
-    <t>maison_medicale_du_champy_simulation_14</t>
-  </si>
-  <si>
-    <t>exterior_wall_isolation, window_replacement_DG, floor_isolation, VMC_installation</t>
-  </si>
-  <si>
-    <t>medecine_du_travail</t>
-  </si>
-  <si>
-    <t>medecine_du_travail_simulation_3</t>
-  </si>
-  <si>
-    <t>medecine_du_travail_simulation_8</t>
-  </si>
-  <si>
-    <t>mille_club_des_yvris</t>
-  </si>
-  <si>
-    <t>mille_club_des_yvris_simulation_1</t>
-  </si>
-  <si>
-    <t>mille_club_des_yvris_simulation_10</t>
-  </si>
-  <si>
-    <t>mille_club_des_yvris_simulation_7</t>
-  </si>
-  <si>
-    <t>mpt_des_coteaux</t>
-  </si>
-  <si>
-    <t>mpt_des_coteaux_simulation_8</t>
-  </si>
-  <si>
-    <t>mpt_des_coteaux_simulation_13</t>
-  </si>
-  <si>
-    <t>mpt_du_champy</t>
-  </si>
-  <si>
-    <t>mpt_du_champy_simulation_4</t>
-  </si>
-  <si>
-    <t>mpt_du_champy_simulation_9</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, window_replacement_TG</t>
-  </si>
-  <si>
-    <t>mpt_du_champy_simulation_10</t>
-  </si>
-  <si>
-    <t>mpt_jardin_des_sources_-_annexe_maison_pour_tous</t>
-  </si>
-  <si>
-    <t>mpt_jardin_des_sources_-_annexe_maison_pour_tous_simulation_2</t>
-  </si>
-  <si>
-    <t>mpt_jardin_des_sources_-_annexe_maison_pour_tous_simulation_5</t>
-  </si>
-  <si>
-    <t>mpt_la_varenne</t>
-  </si>
-  <si>
-    <t>mpt_la_varenne_simulation 6</t>
-  </si>
-  <si>
-    <t>mpt_la_varenne_simulation 10</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, window_replacement_TG, roof_isolation, system_installation</t>
-  </si>
-  <si>
-    <t>mpt_les_richardets</t>
-  </si>
-  <si>
-    <t>mpt_les_richardets_simulation_5</t>
-  </si>
-  <si>
-    <t>mpt_les_richardets_simulation_10</t>
-  </si>
-  <si>
-    <t>indoor_wall_isolation, window_replacement_DG, roof_isolation</t>
-  </si>
-  <si>
-    <t>mpt_marcel_bou</t>
-  </si>
-  <si>
-    <t>mpt_marcel_bou_simulation 1</t>
-  </si>
-  <si>
-    <t>mpt_marcel_bou_simulation 10</t>
-  </si>
-  <si>
-    <t>window_replacement_TG, floor_isolation, roof_isolation, VMC_installation, system_installation</t>
-  </si>
-  <si>
-    <t>multi_accueil_jean_piaget</t>
-  </si>
-  <si>
     <t>multi_accueil_jean_piaget_simulation_7</t>
   </si>
   <si>
-    <t>indoor_wall_isolation, window_replacement_DG, floor_isolation, VMC_installation</t>
-  </si>
-  <si>
     <t>noisy_connecte</t>
   </si>
   <si>
-    <t>noisy_connecte_simulation_1</t>
+    <t>noisy_connecte_simulation_3</t>
   </si>
   <si>
     <t>noisy_connecte_simulation_2</t>
@@ -881,9 +866,6 @@
   </si>
   <si>
     <t>tir_a_l'arc_simulation_14</t>
-  </si>
-  <si>
-    <t>window_replacement_DG, roof_isolation, VMC_installation</t>
   </si>
   <si>
     <t>villa_cathala</t>
@@ -1267,13 +1249,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="58" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="69.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="78.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1329,7 +1311,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>2031</v>
+        <v>2039</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -1352,7 +1334,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -1364,10 +1346,10 @@
         <v>14</v>
       </c>
       <c r="F4">
-        <v>7.9804000000000208E-2</v>
+        <v>0.29665700000000061</v>
       </c>
       <c r="G4">
-        <v>15241.83</v>
+        <v>10256.240000000011</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1375,7 +1357,7 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -1387,10 +1369,10 @@
         <v>16</v>
       </c>
       <c r="F5">
-        <v>0.30359699999999989</v>
+        <v>8.6743999999999488E-2</v>
       </c>
       <c r="G5">
-        <v>10256.23</v>
+        <v>15241.82</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -1398,7 +1380,7 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -1407,13 +1389,13 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>0.41662665725291959</v>
+        <v>1.737361216144141</v>
       </c>
       <c r="G6">
-        <v>11619.203777770879</v>
+        <v>77747.479644143328</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1421,7 +1403,7 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>2046</v>
+        <v>2050</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -1433,10 +1415,10 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>2.903150423451478</v>
+        <v>1.5824158645602571</v>
       </c>
       <c r="G7">
-        <v>229848.70183316339</v>
+        <v>163720.42596679099</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1444,7 +1426,7 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -1467,7 +1449,7 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -1490,7 +1472,7 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -1502,10 +1484,10 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>105.8898961906871</v>
+        <v>662.74619100095333</v>
       </c>
       <c r="G10">
-        <v>31415</v>
+        <v>1635030.88</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1513,7 +1495,7 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>2029</v>
+        <v>2043</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
@@ -1522,182 +1504,182 @@
         <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>556.85629481026626</v>
+        <v>13.138072567843439</v>
       </c>
       <c r="G11">
-        <v>1603615.88</v>
+        <v>360526.58000000007</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B12">
-        <v>2046</v>
+        <v>2028</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
         <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>13.138072567843439</v>
+        <v>10.549939999999999</v>
       </c>
       <c r="G12">
-        <v>360526.58000000007</v>
+        <v>12838.63</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>10.549939999999999</v>
+        <v>3.0657369999999999</v>
       </c>
       <c r="G13">
-        <v>12838.63</v>
+        <v>15193.07</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>3.0657369999999999</v>
+        <v>1.354255717228706</v>
       </c>
       <c r="G14">
-        <v>15193.07</v>
+        <v>6953.9429554892286</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15">
+        <v>2050</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
         <v>35</v>
       </c>
-      <c r="B15">
-        <v>2038</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>2.198377324288463</v>
+        <v>1.5061945865572299</v>
       </c>
       <c r="G15">
-        <v>17998.74616625081</v>
+        <v>36542.594047555423</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16">
-        <v>2049</v>
+        <v>2038</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
         <v>38</v>
       </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
       <c r="F16">
-        <v>0.66207297949747312</v>
+        <v>8.7319300304899485</v>
       </c>
       <c r="G16">
-        <v>25497.790836793829</v>
+        <v>74831.110999529876</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>2039</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
         <v>39</v>
       </c>
-      <c r="B17">
-        <v>2038</v>
-      </c>
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>40</v>
       </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
       <c r="F17">
-        <v>6.0585957890707496</v>
+        <v>11.822330651078561</v>
       </c>
       <c r="G17">
-        <v>49887.407333019917</v>
+        <v>91739.543254106029</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18">
-        <v>2040</v>
+        <v>2029</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
         <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F18">
-        <v>9.4080758459859304</v>
+        <v>9.0161418532178637</v>
       </c>
       <c r="G18">
-        <v>50426.534056448887</v>
+        <v>26123.489479635879</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B19">
-        <v>2049</v>
+        <v>2040</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
@@ -1709,211 +1691,211 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>5.0875890465118303</v>
+        <v>3.545303145349497</v>
       </c>
       <c r="G19">
-        <v>66256.712864167101</v>
+        <v>38704.768869205851</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20">
+        <v>2049</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
         <v>44</v>
       </c>
-      <c r="B20">
-        <v>2030</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" t="s">
-        <v>45</v>
-      </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F20">
-        <v>9.0161418532178637</v>
+        <v>4.6318657097120592</v>
       </c>
       <c r="G20">
-        <v>26123.489479635879</v>
+        <v>91011.902598572968</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
         <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F21">
-        <v>3.545303145349497</v>
+        <v>63.596638105635982</v>
       </c>
       <c r="G21">
-        <v>38704.768869205851</v>
+        <v>358316.06430169212</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B22">
-        <v>2047</v>
+        <v>2040</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22">
-        <v>4.6318657097120592</v>
+        <v>5.10568761640247</v>
       </c>
       <c r="G22">
-        <v>91011.902598572968</v>
+        <v>76646.895491234856</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23">
-        <v>2034</v>
+        <v>2047</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>63.596638105635982</v>
+        <v>1.462280986213123</v>
       </c>
       <c r="G23">
-        <v>358316.06430169212</v>
+        <v>43254.39062903935</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>2048</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" t="s">
         <v>51</v>
       </c>
-      <c r="B24">
-        <v>2042</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>52</v>
       </c>
-      <c r="E24" t="s">
-        <v>53</v>
-      </c>
       <c r="F24">
-        <v>5.10568761640247</v>
+        <v>0.73115156282085625</v>
       </c>
       <c r="G24">
-        <v>76646.895491234856</v>
+        <v>63872.412909362392</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B25">
-        <v>2048</v>
+        <v>2026</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
         <v>54</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>2.1934325490339792</v>
+        <v>2.1865290942851998</v>
       </c>
       <c r="G25">
-        <v>107126.8035384017</v>
+        <v>7940.6048139984969</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26">
+        <v>2035</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" t="s">
         <v>56</v>
       </c>
-      <c r="B26">
-        <v>2032</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
       <c r="F26">
-        <v>2.8838081015796622</v>
+        <v>0.95655345903142397</v>
       </c>
       <c r="G26">
-        <v>16303.996149263039</v>
+        <v>9206.9625313485449</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B27">
         <v>2038</v>
       </c>
       <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" t="s">
         <v>57</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>58</v>
       </c>
-      <c r="E27" t="s">
-        <v>59</v>
-      </c>
       <c r="F27">
-        <v>3.834896639431292</v>
+        <v>3.5756221876943308</v>
       </c>
       <c r="G27">
-        <v>23285.54236624606</v>
+        <v>22441.971170162062</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B28">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" t="s">
         <v>61</v>
-      </c>
-      <c r="E28" t="s">
-        <v>62</v>
       </c>
       <c r="F28">
         <v>194.51479701168859</v>
@@ -1924,19 +1906,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29">
+        <v>2046</v>
+      </c>
+      <c r="C29" t="s">
         <v>60</v>
       </c>
-      <c r="B29">
-        <v>2042</v>
-      </c>
-      <c r="C29" t="s">
-        <v>61</v>
-      </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F29">
         <v>1.025340261888118</v>
@@ -1947,25 +1929,25 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B30">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>1.9190441588806879</v>
+        <v>3.2846222994018528</v>
       </c>
       <c r="G30">
-        <v>38503.605912924373</v>
+        <v>169732.86386919409</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1973,111 +1955,111 @@
         <v>65</v>
       </c>
       <c r="B31">
-        <v>2048</v>
+        <v>2027</v>
       </c>
       <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
         <v>66</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>67</v>
       </c>
-      <c r="E31" t="s">
-        <v>16</v>
-      </c>
       <c r="F31">
-        <v>1.3655781405211651</v>
+        <v>17.081219285695621</v>
       </c>
       <c r="G31">
-        <v>131229.25795626969</v>
+        <v>28304.6</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32">
+        <v>2034</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
         <v>68</v>
       </c>
-      <c r="B32">
-        <v>2027</v>
-      </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" t="s">
-        <v>69</v>
-      </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F32">
-        <v>17.081219285695621</v>
+        <v>8.4016283734344803</v>
       </c>
       <c r="G32">
-        <v>28304.6</v>
+        <v>88764.93</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33">
+        <v>2049</v>
+      </c>
+      <c r="C33" t="s">
         <v>68</v>
       </c>
-      <c r="B33">
-        <v>2036</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>69</v>
       </c>
-      <c r="D33" t="s">
-        <v>70</v>
-      </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F33">
-        <v>8.4016283734344803</v>
+        <v>11.907217237282939</v>
       </c>
       <c r="G33">
-        <v>88764.93</v>
+        <v>300366.61</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B34">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
         <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>11.907217237282939</v>
+        <v>1.134320000000002</v>
       </c>
       <c r="G34">
-        <v>300366.61</v>
+        <v>17569.169999999998</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35">
+        <v>2048</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
         <v>72</v>
       </c>
-      <c r="B35">
-        <v>2041</v>
-      </c>
-      <c r="C35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" t="s">
-        <v>73</v>
-      </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F35">
-        <v>2.1261700000000019</v>
+        <v>2.0619299999999972</v>
       </c>
       <c r="G35">
         <v>78647.19</v>
@@ -2085,13 +2067,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36">
-        <v>2046</v>
+        <v>2026</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -2100,326 +2082,326 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>1.070079999999997</v>
+        <v>23.230140000000009</v>
       </c>
       <c r="G36">
-        <v>17569.169999999998</v>
+        <v>53206.98</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37">
+        <v>2039</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" t="s">
         <v>75</v>
       </c>
-      <c r="B37">
-        <v>2029</v>
-      </c>
-      <c r="C37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" t="s">
-        <v>76</v>
-      </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F37">
-        <v>23.230140000000009</v>
+        <v>42.778629999999993</v>
       </c>
       <c r="G37">
-        <v>53206.98</v>
+        <v>259016.22</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="s">
         <v>75</v>
       </c>
-      <c r="B38">
-        <v>2034</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>76</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>77</v>
       </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
       <c r="F38">
-        <v>42.778629999999993</v>
+        <v>17.47202999999999</v>
       </c>
       <c r="G38">
-        <v>259016.22</v>
+        <v>409172.99999999988</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B39">
-        <v>2048</v>
+        <v>2027</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F39">
-        <v>17.47202999999999</v>
+        <v>13.59935784782127</v>
       </c>
       <c r="G39">
-        <v>409172.99999999988</v>
+        <v>44686.019233865438</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B40">
         <v>2028</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F40">
-        <v>13.59935784782127</v>
+        <v>9.2552720933424908</v>
       </c>
       <c r="G40">
-        <v>44686.019233865438</v>
+        <v>33100.75498804848</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41">
+        <v>2037</v>
+      </c>
+      <c r="C41" t="s">
         <v>80</v>
       </c>
-      <c r="B41">
-        <v>2039</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>81</v>
-      </c>
-      <c r="D41" t="s">
-        <v>82</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
       </c>
       <c r="F41">
-        <v>2.2291739713592702</v>
+        <v>2.10989842878362</v>
       </c>
       <c r="G41">
-        <v>8284.9807661345621</v>
+        <v>8284.2257780860818</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B42">
         <v>2040</v>
       </c>
       <c r="C42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" t="s">
         <v>82</v>
-      </c>
-      <c r="D42" t="s">
-        <v>83</v>
       </c>
       <c r="E42" t="s">
         <v>16</v>
       </c>
       <c r="F42">
-        <v>9.1359965507668406</v>
+        <v>3.3721659576688299</v>
       </c>
       <c r="G42">
-        <v>33100</v>
+        <v>49631</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B43">
-        <v>2041</v>
+        <v>2029</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
         <v>84</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F43">
-        <v>3.3721659576688299</v>
+        <v>27.444479999999999</v>
       </c>
       <c r="G43">
-        <v>49631</v>
+        <v>11056.420733999999</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44">
+        <v>2044</v>
+      </c>
+      <c r="C44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" t="s">
         <v>85</v>
       </c>
-      <c r="B44">
-        <v>2027</v>
-      </c>
-      <c r="C44" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>86</v>
       </c>
-      <c r="E44" t="s">
-        <v>27</v>
-      </c>
       <c r="F44">
-        <v>27.444479999999999</v>
+        <v>4.1056699999999999</v>
       </c>
       <c r="G44">
-        <v>11056.420733999999</v>
+        <v>443046.57926600002</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B45">
-        <v>2042</v>
+        <v>2026</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F45">
-        <v>3.7054200000000002</v>
+        <v>64.610087354885991</v>
       </c>
       <c r="G45">
-        <v>252094.57926599999</v>
+        <v>9273.1737723880597</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B46">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="C46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="F46">
-        <v>0.40024999999999977</v>
+        <v>-51.920088032505703</v>
       </c>
       <c r="G46">
-        <v>190952</v>
+        <v>209457.53622761191</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47">
+        <v>2049</v>
+      </c>
+      <c r="C47" t="s">
         <v>89</v>
       </c>
-      <c r="B47">
-        <v>2030</v>
-      </c>
-      <c r="C47" t="s">
-        <v>8</v>
-      </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F47">
-        <v>64.610087354885991</v>
+        <v>52.69522126425997</v>
       </c>
       <c r="G47">
-        <v>9273.1737723880597</v>
+        <v>282935.09999999998</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B48">
-        <v>2041</v>
+        <v>2028</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E48" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F48">
-        <v>0.77513323175426763</v>
+        <v>1.9922955597117531</v>
       </c>
       <c r="G48">
-        <v>492392.63622761192</v>
+        <v>6735.6568326403212</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49">
+        <v>2034</v>
+      </c>
+      <c r="C49" t="s">
         <v>93</v>
-      </c>
-      <c r="B49">
-        <v>2033</v>
-      </c>
-      <c r="C49" t="s">
-        <v>8</v>
       </c>
       <c r="D49" t="s">
         <v>94</v>
       </c>
       <c r="E49" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="F49">
-        <v>3.754276376311632</v>
+        <v>1.7619808165998789</v>
       </c>
       <c r="G49">
-        <v>21876.120645020401</v>
+        <v>15140.46381238008</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B50">
-        <v>2041</v>
+        <v>2045</v>
       </c>
       <c r="C50" t="s">
         <v>94</v>
       </c>
       <c r="D50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E50" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F50">
         <v>2.4817458827388169E-2</v>
@@ -2430,16 +2412,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
@@ -2453,48 +2435,48 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52">
+        <v>2050</v>
+      </c>
+      <c r="C52" t="s">
         <v>97</v>
       </c>
-      <c r="B52">
-        <v>2042</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>98</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>99</v>
       </c>
-      <c r="E52" t="s">
-        <v>14</v>
-      </c>
       <c r="F52">
-        <v>1.0740298759646409</v>
+        <v>7.4068727749157226</v>
       </c>
       <c r="G52">
-        <v>82466.49148218878</v>
+        <v>199575.06243967259</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B53">
-        <v>2046</v>
+        <v>2037</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E53" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="F53">
-        <v>6.3328428989510819</v>
+        <v>356.1949078886289</v>
       </c>
       <c r="G53">
-        <v>117108.5709574838</v>
+        <v>1734957.675</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -2502,7 +2484,7 @@
         <v>102</v>
       </c>
       <c r="B54">
-        <v>2038</v>
+        <v>2030</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
@@ -2511,128 +2493,128 @@
         <v>103</v>
       </c>
       <c r="E54" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="F54">
-        <v>356.1949078886289</v>
+        <v>243.02685</v>
       </c>
       <c r="G54">
-        <v>1734957.675</v>
+        <v>573223.78451999999</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B55">
-        <v>2028</v>
+        <v>2044</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D55" t="s">
         <v>105</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="F55">
-        <v>243.02685</v>
+        <v>5.8000000001356966E-4</v>
       </c>
       <c r="G55">
-        <v>573223.78451999999</v>
+        <v>866719.68547999999</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B56">
-        <v>2046</v>
+        <v>2027</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D56" t="s">
         <v>107</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="F56">
-        <v>-108.38536000000001</v>
+        <v>361.21949999999998</v>
       </c>
       <c r="G56">
-        <v>519440.72548000002</v>
+        <v>649628.80000000005</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B57">
-        <v>2050</v>
+        <v>2029</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E57" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="F57">
-        <v>108.38594000000001</v>
+        <v>328.67354</v>
       </c>
       <c r="G57">
-        <v>347278.96</v>
+        <v>818360.55200000003</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B58">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C58" t="s">
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E58" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F58">
-        <v>361.21949999999998</v>
+        <v>322.37128999999999</v>
       </c>
       <c r="G58">
-        <v>649628.80000000005</v>
+        <v>573049.86800000002</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B59">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F59">
-        <v>328.67354</v>
+        <v>210.15208699999999</v>
       </c>
       <c r="G59">
-        <v>818360.55200000003</v>
+        <v>307702</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -2640,91 +2622,91 @@
         <v>115</v>
       </c>
       <c r="B60">
-        <v>2027</v>
+        <v>2048</v>
       </c>
       <c r="C60" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="D60" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="F60">
-        <v>322.37128999999999</v>
+        <v>29.978242999999988</v>
       </c>
       <c r="G60">
-        <v>573049.86800000002</v>
+        <v>842292.79813400004</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B61">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E61" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="F61">
-        <v>210.15208699999999</v>
+        <v>28.54177181333705</v>
       </c>
       <c r="G61">
-        <v>307702</v>
+        <v>26071.4</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B62">
-        <v>2047</v>
+        <v>2035</v>
       </c>
       <c r="C62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D62" t="s">
         <v>121</v>
       </c>
       <c r="E62" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="F62">
-        <v>22.523036000000019</v>
+        <v>159.83840490120889</v>
       </c>
       <c r="G62">
-        <v>540428</v>
+        <v>1370808.4</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B63">
-        <v>2048</v>
+        <v>2029</v>
       </c>
       <c r="C63" t="s">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E63" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F63">
-        <v>7.455206999999973</v>
+        <v>146.66415590514021</v>
       </c>
       <c r="G63">
-        <v>301864.79813399998</v>
+        <v>103932.1125</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -2732,45 +2714,45 @@
         <v>123</v>
       </c>
       <c r="B64">
-        <v>2029</v>
+        <v>2038</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E64" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="F64">
-        <v>28.54177181333705</v>
+        <v>160.9976025042391</v>
       </c>
       <c r="G64">
-        <v>26071.4</v>
+        <v>1567792.8</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B65">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="D65" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E65" t="s">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="F65">
-        <v>159.83840490120889</v>
+        <v>40.228467489450217</v>
       </c>
       <c r="G65">
-        <v>1370808.4</v>
+        <v>100120.6125</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
@@ -2778,2367 +2760,2183 @@
         <v>127</v>
       </c>
       <c r="B66">
-        <v>2026</v>
+        <v>2039</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="F66">
-        <v>146.66415590514021</v>
+        <v>112.2340451549701</v>
       </c>
       <c r="G66">
-        <v>103932.1125</v>
+        <v>820634.28749999998</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B67">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="C67" t="s">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="D67" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E67" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="F67">
-        <v>66.442950767644987</v>
+        <v>112.2760216599179</v>
       </c>
       <c r="G67">
-        <v>660930.25</v>
+        <v>774587.53749999998</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B68">
-        <v>2036</v>
+        <v>2043</v>
       </c>
       <c r="C68" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D68" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="F68">
-        <v>94.554651736594082</v>
+        <v>19.374301022169689</v>
       </c>
       <c r="G68">
-        <v>906862.55</v>
+        <v>968916.46250000002</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B69">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E69" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="F69">
-        <v>40.228467489450217</v>
+        <v>137.87237485893729</v>
       </c>
       <c r="G69">
-        <v>100120.6125</v>
+        <v>266245.38</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B70">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="C70" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D70" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E70" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F70">
-        <v>75.655724313530072</v>
+        <v>132.47975470533001</v>
       </c>
       <c r="G70">
-        <v>505473.22749999998</v>
+        <v>991739.24999999988</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B71">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="C71" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E71" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="F71">
-        <v>16.860262721759</v>
+        <v>619.48361081937708</v>
       </c>
       <c r="G71">
-        <v>91784.979999999981</v>
+        <v>646264</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B72">
-        <v>2040</v>
+        <v>2033</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D72" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E72" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F72">
-        <v>19.71805811968099</v>
+        <v>110.0214620667509</v>
       </c>
       <c r="G72">
-        <v>223376.0800000001</v>
+        <v>659675.32499999995</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B73">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="C73" t="s">
         <v>8</v>
       </c>
       <c r="D73" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E73" t="s">
-        <v>139</v>
+        <v>56</v>
       </c>
       <c r="F73">
-        <v>112.2760216599179</v>
+        <v>104.32370045429001</v>
       </c>
       <c r="G73">
-        <v>774587.53749999998</v>
+        <v>579250</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B74">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D74" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E74" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F74">
-        <v>19.374301022169689</v>
+        <v>106.229531584965</v>
       </c>
       <c r="G74">
-        <v>968916.46250000002</v>
+        <v>1977043.6665000001</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B75">
-        <v>2027</v>
+        <v>2047</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="D75" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E75" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F75">
-        <v>137.87237485893729</v>
+        <v>41.073904387543003</v>
       </c>
       <c r="G75">
-        <v>266245.38</v>
+        <v>301322.52350000013</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B76">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="C76" t="s">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="F76">
-        <v>132.47975470533001</v>
+        <v>214.86475652604699</v>
       </c>
       <c r="G76">
-        <v>991739.24999999988</v>
+        <v>461835</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B77">
-        <v>2030</v>
+        <v>2036</v>
       </c>
       <c r="C77" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="D77" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E77" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="F77">
-        <v>619.48361081937708</v>
+        <v>138.35159584764301</v>
       </c>
       <c r="G77">
-        <v>646264</v>
+        <v>1362949.4</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B78">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="C78" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D78" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E78" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F78">
-        <v>110.0214620667509</v>
+        <v>66.536278947562039</v>
       </c>
       <c r="G78">
-        <v>659675.32499999995</v>
+        <v>506550</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B79">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
       </c>
       <c r="D79" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E79" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F79">
-        <v>27.868697599388948</v>
+        <v>63.565737493575057</v>
       </c>
       <c r="G79">
-        <v>48961.7</v>
+        <v>68502.2</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B80">
-        <v>2039</v>
+        <v>2027</v>
       </c>
       <c r="C80" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D80" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E80" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F80">
-        <v>109.84122601263201</v>
+        <v>210.07714856061889</v>
       </c>
       <c r="G80">
-        <v>1966056.27</v>
+        <v>702573.37</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B81">
-        <v>2040</v>
+        <v>2046</v>
       </c>
       <c r="C81" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D81" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E81" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F81">
-        <v>113.917212814777</v>
+        <v>110.32785466571001</v>
       </c>
       <c r="G81">
-        <v>842598.22</v>
+        <v>1608871.8</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B82">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E82" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F82">
-        <v>214.86475652604699</v>
+        <v>168.549483343839</v>
       </c>
       <c r="G82">
-        <v>461835</v>
+        <v>333163.47600000002</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B83">
-        <v>2037</v>
+        <v>2033</v>
       </c>
       <c r="C83" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D83" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E83" t="s">
-        <v>48</v>
+        <v>159</v>
       </c>
       <c r="F83">
-        <v>140.93328782152301</v>
+        <v>143.9480955597287</v>
       </c>
       <c r="G83">
-        <v>928724.39999999991</v>
+        <v>1334722.32</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B84">
-        <v>2049</v>
+        <v>2030</v>
       </c>
       <c r="C84" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D84" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F84">
-        <v>63.954586973682012</v>
+        <v>60.655157234046698</v>
       </c>
       <c r="G84">
-        <v>940775</v>
+        <v>81304.2</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B85">
-        <v>2028</v>
+        <v>2034</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E85" t="s">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="F85">
-        <v>273.64288605419398</v>
+        <v>70.5526423536202</v>
       </c>
       <c r="G85">
-        <v>771075.57</v>
+        <v>654787.19999999995</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B86">
-        <v>2045</v>
+        <v>2027</v>
       </c>
       <c r="C86" t="s">
-        <v>157</v>
+        <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E86" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="F86">
-        <v>110.32785466571001</v>
+        <v>172.03790279504199</v>
       </c>
       <c r="G86">
-        <v>1608871.8</v>
+        <v>176451.75</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B87">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="D87" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E87" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
       <c r="F87">
-        <v>168.549483343839</v>
+        <v>202.312031375359</v>
       </c>
       <c r="G87">
-        <v>333163.47600000002</v>
+        <v>763059.87</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B88">
-        <v>2036</v>
+        <v>2047</v>
       </c>
       <c r="C88" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D88" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E88" t="s">
-        <v>163</v>
+        <v>16</v>
       </c>
       <c r="F88">
-        <v>65.169231533688702</v>
+        <v>30.88628312119079</v>
       </c>
       <c r="G88">
-        <v>304143.54399999999</v>
+        <v>860125.25999999989</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B89">
-        <v>2050</v>
+        <v>2028</v>
       </c>
       <c r="C89" t="s">
-        <v>162</v>
+        <v>8</v>
       </c>
       <c r="D89" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E89" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="F89">
-        <v>78.778864026040026</v>
+        <v>166.0758942785142</v>
       </c>
       <c r="G89">
-        <v>1030578.776</v>
+        <v>355978.8</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B90">
-        <v>2027</v>
+        <v>2040</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>169</v>
       </c>
       <c r="D90" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="F90">
-        <v>60.655157234046698</v>
+        <v>142.24625615321571</v>
       </c>
       <c r="G90">
-        <v>81304.2</v>
+        <v>1335247</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B91">
-        <v>2040</v>
+        <v>2028</v>
       </c>
       <c r="C91" t="s">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="D91" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E91" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="F91">
-        <v>70.5526423536202</v>
+        <v>97.45402069972728</v>
       </c>
       <c r="G91">
-        <v>654787.19999999995</v>
+        <v>228505.05</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B92">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="D92" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="F92">
-        <v>172.03790279504199</v>
+        <v>116.7805619031478</v>
       </c>
       <c r="G92">
-        <v>176451.75</v>
+        <v>1085270.21</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B93">
-        <v>2037</v>
+        <v>2030</v>
       </c>
       <c r="C93" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="D93" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E93" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="F93">
-        <v>202.312031375359</v>
+        <v>123.84193813187829</v>
       </c>
       <c r="G93">
-        <v>763059.87</v>
+        <v>272250.12</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B94">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="C94" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D94" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E94" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F94">
-        <v>30.88628312119079</v>
+        <v>15.508364066219199</v>
       </c>
       <c r="G94">
-        <v>860125.25999999989</v>
+        <v>644591.30000000005</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B95">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C95" t="s">
         <v>8</v>
       </c>
       <c r="D95" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E95" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F95">
-        <v>166.0758942785142</v>
+        <v>156.97550000000001</v>
       </c>
       <c r="G95">
-        <v>355978.8</v>
+        <v>38515.465943000003</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B96">
-        <v>2035</v>
+        <v>2042</v>
       </c>
       <c r="C96" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D96" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E96" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="F96">
-        <v>142.24625615321571</v>
+        <v>26.301199999999991</v>
       </c>
       <c r="G96">
-        <v>1335247</v>
+        <v>1436403.314057</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B97">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="C97" t="s">
         <v>8</v>
       </c>
       <c r="D97" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F97">
-        <v>97.45402069972728</v>
+        <v>14.857799999999999</v>
       </c>
       <c r="G97">
-        <v>228505.05</v>
+        <v>569215.19999999995</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B98">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="C98" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E98" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="F98">
-        <v>116.7805619031478</v>
+        <v>124.43746623257</v>
       </c>
       <c r="G98">
-        <v>1085270.21</v>
+        <v>238050</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B99">
-        <v>2030</v>
+        <v>2050</v>
       </c>
       <c r="C99" t="s">
-        <v>8</v>
+        <v>186</v>
       </c>
       <c r="D99" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E99" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F99">
-        <v>123.84193813187829</v>
+        <v>18.583109556676089</v>
       </c>
       <c r="G99">
-        <v>272250.12</v>
+        <v>599143.69999999995</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B100">
-        <v>2046</v>
+        <v>2027</v>
       </c>
       <c r="C100" t="s">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="D100" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E100" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F100">
-        <v>-1.1606051536600011</v>
+        <v>22.90961999999999</v>
       </c>
       <c r="G100">
-        <v>224508.2</v>
+        <v>57632.4</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B101">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="C101" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D101" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E101" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="F101">
-        <v>16.668969219879202</v>
+        <v>7.3322000000000003</v>
       </c>
       <c r="G101">
-        <v>420083.1</v>
+        <v>329068.79999999999</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B102">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="C102" t="s">
         <v>8</v>
       </c>
       <c r="D102" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E102" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F102">
-        <v>156.97550000000001</v>
+        <v>73.917410000000018</v>
       </c>
       <c r="G102">
-        <v>38515.465943000003</v>
+        <v>69747.91</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B103">
-        <v>2043</v>
+        <v>2032</v>
       </c>
       <c r="C103" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D103" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F103">
-        <v>26.30019999999999</v>
+        <v>28.11838999999998</v>
       </c>
       <c r="G103">
-        <v>1325653.314057</v>
+        <v>142300.19899999999</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B104">
-        <v>2048</v>
+        <v>2034</v>
       </c>
       <c r="C104" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D104" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E104" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="F104">
-        <v>1.0000000000047751E-3</v>
+        <v>75.213210000000004</v>
       </c>
       <c r="G104">
-        <v>110750</v>
+        <v>202020.74100000001</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B105">
-        <v>2049</v>
+        <v>2026</v>
       </c>
       <c r="C105" t="s">
         <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E105" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F105">
-        <v>14.857799999999999</v>
+        <v>73.597017894566108</v>
       </c>
       <c r="G105">
-        <v>569215.19999999995</v>
+        <v>133100</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B106">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="D106" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E106" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="F106">
-        <v>124.43746623257</v>
+        <v>128.38059522356599</v>
       </c>
       <c r="G106">
-        <v>238050</v>
+        <v>687649.2</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B107">
-        <v>2046</v>
+        <v>2028</v>
       </c>
       <c r="C107" t="s">
-        <v>192</v>
+        <v>8</v>
       </c>
       <c r="D107" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E107" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>45.029677638955022</v>
       </c>
       <c r="G107">
-        <v>8623.5</v>
+        <v>78050.264460705075</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B108">
-        <v>2047</v>
+        <v>2030</v>
       </c>
       <c r="C108" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D108" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E108" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F108">
-        <v>18.583109556676089</v>
+        <v>9.1249849348097314</v>
       </c>
       <c r="G108">
-        <v>590520.19999999995</v>
+        <v>10987.985539294919</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B109">
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="C109" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="D109" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E109" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F109">
-        <v>22.90961999999999</v>
+        <v>29.4501933938223</v>
       </c>
       <c r="G109">
-        <v>57632.4</v>
+        <v>244860.483405065</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B110">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="C110" t="s">
-        <v>196</v>
+        <v>8</v>
       </c>
       <c r="D110" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E110" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F110">
-        <v>5.92117</v>
+        <v>0.84129237939744161</v>
       </c>
       <c r="G110">
-        <v>211318.8</v>
+        <v>9341.4002812991912</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B111">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="C111" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D111" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E111" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="F111">
-        <v>1.41103</v>
+        <v>0.21149375100199941</v>
       </c>
       <c r="G111">
-        <v>117750</v>
+        <v>61884.029541900672</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B112">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C112" t="s">
         <v>8</v>
       </c>
       <c r="D112" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
       </c>
       <c r="F112">
-        <v>73.917410000000018</v>
+        <v>5.0857900000000029</v>
       </c>
       <c r="G112">
-        <v>69747.91</v>
+        <v>15402.11</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B113">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="C113" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D113" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E113" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F113">
-        <v>103.33159999999999</v>
+        <v>6.8878399999999971</v>
       </c>
       <c r="G113">
-        <v>344320.93999999989</v>
+        <v>45029.73</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B114">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="C114" t="s">
         <v>8</v>
       </c>
       <c r="D114" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E114" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F114">
-        <v>73.597017894566108</v>
+        <v>5.3192298155530366</v>
       </c>
       <c r="G114">
-        <v>133100</v>
+        <v>12986.24608279649</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B115">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="C115" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D115" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E115" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="F115">
-        <v>128.38059522356599</v>
+        <v>5.4188617104797228</v>
       </c>
       <c r="G115">
-        <v>687649.2</v>
+        <v>57305.47422814805</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B116">
-        <v>2028</v>
+        <v>2042</v>
       </c>
       <c r="C116" t="s">
-        <v>8</v>
+        <v>212</v>
       </c>
       <c r="D116" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E116" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="F116">
-        <v>45.029677638955022</v>
+        <v>6.8177414535394494</v>
       </c>
       <c r="G116">
-        <v>78050.264460705075</v>
+        <v>121344.01956307171</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B117">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="C117" t="s">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="D117" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E117" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F117">
-        <v>9.1249849348097314</v>
+        <v>1.06301</v>
       </c>
       <c r="G117">
-        <v>10987.985539294919</v>
+        <v>24740.71</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B118">
-        <v>2035</v>
+        <v>2048</v>
       </c>
       <c r="C118" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D118" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E118" t="s">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="F118">
-        <v>29.4501933938223</v>
+        <v>3.3023769999999999</v>
       </c>
       <c r="G118">
-        <v>244860.483405065</v>
+        <v>154332.99</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B119">
-        <v>2040</v>
+        <v>2048</v>
       </c>
       <c r="C119" t="s">
         <v>8</v>
       </c>
       <c r="D119" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E119" t="s">
-        <v>10</v>
+        <v>220</v>
       </c>
       <c r="F119">
-        <v>0.84129237939744161</v>
+        <v>8.7928260437898693</v>
       </c>
       <c r="G119">
-        <v>9341.4002812991912</v>
+        <v>185904.2163574789</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B120">
-        <v>2044</v>
+        <v>2049</v>
       </c>
       <c r="C120" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D120" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E120" t="s">
-        <v>213</v>
+        <v>16</v>
       </c>
       <c r="F120">
-        <v>0.21149375100199941</v>
+        <v>1.5315632740522001</v>
       </c>
       <c r="G120">
-        <v>61884.029541900672</v>
+        <v>106073.1370885404</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B121">
-        <v>2026</v>
+        <v>2037</v>
       </c>
       <c r="C121" t="s">
         <v>8</v>
       </c>
       <c r="D121" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E121" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="F121">
-        <v>5.0857900000000029</v>
+        <v>6.8459569869175212</v>
       </c>
       <c r="G121">
-        <v>15402.11</v>
+        <v>54973.59435801323</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B122">
-        <v>2031</v>
+        <v>2049</v>
       </c>
       <c r="C122" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D122" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="E122" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="F122">
-        <v>2.694229999999997</v>
+        <v>4.0601902056852079</v>
       </c>
       <c r="G122">
-        <v>23085.21</v>
+        <v>71935.517049553673</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B123">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="C123" t="s">
-        <v>216</v>
+        <v>8</v>
       </c>
       <c r="D123" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E123" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F123">
-        <v>4.1936099999999996</v>
+        <v>0.92327100426064124</v>
       </c>
       <c r="G123">
-        <v>21944.52</v>
+        <v>16433.072570775072</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B124">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="C124" t="s">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="D124" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E124" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F124">
-        <v>5.3192298155530366</v>
+        <v>5.6874140166173994</v>
       </c>
       <c r="G124">
-        <v>12986.24608279649</v>
+        <v>57840.802350333033</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B125">
         <v>2050</v>
       </c>
       <c r="C125" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D125" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E125" t="s">
-        <v>221</v>
+        <v>16</v>
       </c>
       <c r="F125">
-        <v>12.23660316401917</v>
+        <v>2.5902092070017808</v>
       </c>
       <c r="G125">
-        <v>178649.49379121969</v>
+        <v>89197.135243616794</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B126">
-        <v>2049</v>
+        <v>2037</v>
       </c>
       <c r="C126" t="s">
         <v>8</v>
       </c>
       <c r="D126" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E126" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="F126">
-        <v>1.7874599999999989</v>
+        <v>16.660058670938941</v>
       </c>
       <c r="G126">
-        <v>74612.91</v>
+        <v>120454.0399502306</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B127">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="C127" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D127" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E127" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="F127">
-        <v>2.5779270000000012</v>
+        <v>1.3479147329330099</v>
       </c>
       <c r="G127">
-        <v>104460.79</v>
+        <v>82040.732074304804</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B128">
-        <v>2043</v>
+        <v>2027</v>
       </c>
       <c r="C128" t="s">
         <v>8</v>
       </c>
       <c r="D128" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E128" t="s">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="F128">
-        <v>10.324389317842069</v>
+        <v>33.175050000000013</v>
       </c>
       <c r="G128">
-        <v>291977.35344601929</v>
+        <v>71000</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B129">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="C129" t="s">
-        <v>8</v>
+        <v>233</v>
       </c>
       <c r="D129" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E129" t="s">
-        <v>139</v>
+        <v>235</v>
       </c>
       <c r="F129">
-        <v>6.8459569869175212</v>
+        <v>2.5022699999999891</v>
       </c>
       <c r="G129">
-        <v>54973.59435801323</v>
+        <v>457551.45199999987</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B130">
         <v>2045</v>
       </c>
       <c r="C130" t="s">
-        <v>229</v>
+        <v>8</v>
       </c>
       <c r="D130" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E130" t="s">
-        <v>101</v>
+        <v>238</v>
       </c>
       <c r="F130">
-        <v>4.0601902056852079</v>
+        <v>10.348367579621589</v>
       </c>
       <c r="G130">
-        <v>71935.517049553673</v>
+        <v>1230328.272410715</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B131">
-        <v>2035</v>
+        <v>2028</v>
       </c>
       <c r="C131" t="s">
         <v>8</v>
       </c>
       <c r="D131" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="F131">
-        <v>2.8026181446767602</v>
+        <v>16.3726950353295</v>
       </c>
       <c r="G131">
-        <v>14190.45333421175</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B132">
-        <v>2047</v>
+        <v>2038</v>
       </c>
       <c r="C132" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D132" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E132" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="F132">
-        <v>3.5352787517349218</v>
+        <v>43.177670964028898</v>
       </c>
       <c r="G132">
-        <v>105630.2078143918</v>
+        <v>274952.19</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B133">
-        <v>2048</v>
+        <v>2040</v>
       </c>
       <c r="C133" t="s">
-        <v>233</v>
+        <v>8</v>
       </c>
       <c r="D133" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E133" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F133">
-        <v>2.8629973314681392</v>
+        <v>10.9498</v>
       </c>
       <c r="G133">
-        <v>43650.349016121298</v>
+        <v>92083.26</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B134">
-        <v>2033</v>
+        <v>2042</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
+        <v>244</v>
       </c>
       <c r="D134" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E134" t="s">
-        <v>117</v>
+        <v>246</v>
       </c>
       <c r="F134">
-        <v>16.660058670938941</v>
+        <v>10.65570000000001</v>
       </c>
       <c r="G134">
-        <v>120454.0399502306</v>
+        <v>238574.14</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B135">
-        <v>2041</v>
+        <v>2029</v>
       </c>
       <c r="C135" t="s">
-        <v>236</v>
+        <v>8</v>
       </c>
       <c r="D135" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E135" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F135">
-        <v>1.3479147329330099</v>
+        <v>21.350376415122529</v>
       </c>
       <c r="G135">
-        <v>82040.732074304804</v>
+        <v>27306.720000000001</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B136">
-        <v>2027</v>
+        <v>2037</v>
       </c>
       <c r="C136" t="s">
-        <v>8</v>
+        <v>248</v>
       </c>
       <c r="D136" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E136" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="F136">
-        <v>33.175050000000013</v>
+        <v>14.788299052942371</v>
       </c>
       <c r="G136">
-        <v>71000</v>
+        <v>62471.240000000013</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B137">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="C137" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D137" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="E137" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="F137">
-        <v>2.361969999999999</v>
+        <v>12.247781578591381</v>
       </c>
       <c r="G137">
-        <v>365518.33600000001</v>
+        <v>135533.18</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B138">
-        <v>2049</v>
+        <v>2036</v>
       </c>
       <c r="C138" t="s">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="D138" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E138" t="s">
-        <v>41</v>
+        <v>254</v>
       </c>
       <c r="F138">
-        <v>0.14029999999998921</v>
+        <v>65.149483434267694</v>
       </c>
       <c r="G138">
-        <v>92033.115999999922</v>
+        <v>275781.31594995741</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B139">
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="C139" t="s">
-        <v>8</v>
+        <v>253</v>
       </c>
       <c r="D139" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="E139" t="s">
         <v>16</v>
       </c>
       <c r="F139">
-        <v>1.79162151810857</v>
+        <v>20.654629270324818</v>
       </c>
       <c r="G139">
-        <v>76467.483308186464</v>
+        <v>198630.0299002869</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B140">
-        <v>2044</v>
+        <v>2027</v>
       </c>
       <c r="C140" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="D140" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E140" t="s">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="F140">
-        <v>8.5567460615130191</v>
+        <v>3.1918799999999989</v>
       </c>
       <c r="G140">
-        <v>1153860.789102528</v>
+        <v>8160.415</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B141">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C141" t="s">
-        <v>8</v>
+        <v>257</v>
       </c>
       <c r="D141" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E141" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F141">
-        <v>16.3726950353295</v>
+        <v>5.1008970000000016</v>
       </c>
       <c r="G141">
-        <v>18800</v>
+        <v>5624.585</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B142">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="C142" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D142" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E142" t="s">
-        <v>249</v>
+        <v>52</v>
       </c>
       <c r="F142">
-        <v>43.177670964028898</v>
+        <v>2.299386999999999</v>
       </c>
       <c r="G142">
-        <v>274952.19</v>
+        <v>23817</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B143">
-        <v>2038</v>
+        <v>2030</v>
       </c>
       <c r="C143" t="s">
         <v>8</v>
       </c>
       <c r="D143" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="E143" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F143">
-        <v>10.9498</v>
+        <v>9.7206936774894821</v>
       </c>
       <c r="G143">
-        <v>92083.26</v>
+        <v>26094.599932147201</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B144">
-        <v>2048</v>
+        <v>2036</v>
       </c>
       <c r="C144" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D144" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E144" t="s">
-        <v>253</v>
+        <v>56</v>
       </c>
       <c r="F144">
-        <v>10.65570000000001</v>
+        <v>3.704168062062708</v>
       </c>
       <c r="G144">
-        <v>238574.14</v>
+        <v>26064.525753353599</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B145">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="C145" t="s">
         <v>8</v>
       </c>
       <c r="D145" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E145" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F145">
-        <v>21.350376415122529</v>
+        <v>4.5307606098828286</v>
       </c>
       <c r="G145">
-        <v>27306.720000000001</v>
+        <v>11928.91698947437</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B146">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="C146" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D146" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E146" t="s">
-        <v>257</v>
+        <v>10</v>
       </c>
       <c r="F146">
-        <v>27.03608063153375</v>
+        <v>0.99650126265326211</v>
       </c>
       <c r="G146">
-        <v>198004.42</v>
+        <v>3738.2787459984302</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B147">
-        <v>2032</v>
+        <v>2046</v>
       </c>
       <c r="C147" t="s">
-        <v>8</v>
+        <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E147" t="s">
-        <v>260</v>
+        <v>52</v>
       </c>
       <c r="F147">
-        <v>85.804112704592512</v>
+        <v>1.8587263017232301</v>
       </c>
       <c r="G147">
-        <v>474411.34585024428</v>
+        <v>67289.01742797179</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B148">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C148" t="s">
         <v>8</v>
       </c>
       <c r="D148" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E148" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F148">
-        <v>5.3683899999999998</v>
+        <v>72.393400000000014</v>
       </c>
       <c r="G148">
-        <v>5637.8200892402547</v>
+        <v>123709.6</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B149">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="C149" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D149" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E149" t="s">
         <v>16</v>
       </c>
       <c r="F149">
-        <v>2.9243870000000012</v>
+        <v>11.0436</v>
       </c>
       <c r="G149">
-        <v>8147.1799107597453</v>
+        <v>134640</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B150">
-        <v>2034</v>
+        <v>2027</v>
       </c>
       <c r="C150" t="s">
-        <v>263</v>
+        <v>8</v>
       </c>
       <c r="D150" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E150" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="F150">
-        <v>2.299386999999999</v>
+        <v>55.367043162168223</v>
       </c>
       <c r="G150">
-        <v>23817</v>
+        <v>166915.41610680911</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B151">
-        <v>2027</v>
+        <v>2039</v>
       </c>
       <c r="C151" t="s">
-        <v>8</v>
+        <v>271</v>
       </c>
       <c r="D151" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E151" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F151">
-        <v>9.7206936774894821</v>
+        <v>33.724839340295198</v>
       </c>
       <c r="G151">
-        <v>26094.599932147201</v>
+        <v>179793.75811916459</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B152">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="C152" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D152" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E152" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F152">
-        <v>3.704168062062708</v>
+        <v>6.2393114062221002</v>
       </c>
       <c r="G152">
-        <v>26064.525753353599</v>
+        <v>194197.58348691001</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B153">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C153" t="s">
         <v>8</v>
       </c>
       <c r="D153" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E153" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F153">
-        <v>4.5307606098828286</v>
+        <v>10.162629999999989</v>
       </c>
       <c r="G153">
-        <v>11928.91698947437</v>
+        <v>21960</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B154">
-        <v>2040</v>
+        <v>2036</v>
       </c>
       <c r="C154" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D154" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E154" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F154">
-        <v>0.99650126265326211</v>
+        <v>7.9973500000000124</v>
       </c>
       <c r="G154">
-        <v>3738.2787459984302</v>
+        <v>54879.06</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B155">
-        <v>2049</v>
+        <v>2039</v>
       </c>
       <c r="C155" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D155" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E155" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="F155">
-        <v>1.8587263017232301</v>
+        <v>8.0698099999999897</v>
       </c>
       <c r="G155">
-        <v>67289.01742797179</v>
+        <v>80520.040000000008</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B156">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="C156" t="s">
         <v>8</v>
       </c>
       <c r="D156" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E156" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F156">
-        <v>72.393400000000014</v>
+        <v>5.4219599999999986</v>
       </c>
       <c r="G156">
-        <v>123709.6</v>
+        <v>37831.449999999997</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B157">
-        <v>2032</v>
+        <v>2047</v>
       </c>
       <c r="C157" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D157" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E157" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F157">
-        <v>11.0436</v>
+        <v>8.2250380000000014</v>
       </c>
       <c r="G157">
-        <v>134640</v>
+        <v>374918.95</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B158">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C158" t="s">
         <v>8</v>
       </c>
       <c r="D158" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E158" t="s">
-        <v>139</v>
+        <v>56</v>
       </c>
       <c r="F158">
-        <v>55.367043162168223</v>
+        <v>10.524590706516619</v>
       </c>
       <c r="G158">
-        <v>166915.41610680911</v>
+        <v>21250</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B159">
-        <v>2040</v>
+        <v>2028</v>
       </c>
       <c r="C159" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D159" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E159" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F159">
-        <v>33.724839340295198</v>
+        <v>40.350659988379192</v>
       </c>
       <c r="G159">
-        <v>179793.75811916459</v>
+        <v>48034.200000000012</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B160">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="C160" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D160" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E160" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F160">
-        <v>6.2393114062221002</v>
+        <v>3.9527877778783491</v>
       </c>
       <c r="G160">
-        <v>194197.58348691001</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>279</v>
-      </c>
-      <c r="B161">
-        <v>2027</v>
-      </c>
-      <c r="C161" t="s">
-        <v>8</v>
-      </c>
-      <c r="D161" t="s">
-        <v>280</v>
-      </c>
-      <c r="E161" t="s">
-        <v>10</v>
-      </c>
-      <c r="F161">
-        <v>10.162629999999989</v>
-      </c>
-      <c r="G161">
-        <v>21960</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>279</v>
-      </c>
-      <c r="B162">
-        <v>2037</v>
-      </c>
-      <c r="C162" t="s">
-        <v>280</v>
-      </c>
-      <c r="D162" t="s">
-        <v>281</v>
-      </c>
-      <c r="E162" t="s">
-        <v>12</v>
-      </c>
-      <c r="F162">
-        <v>7.9973500000000124</v>
-      </c>
-      <c r="G162">
-        <v>54879.06</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>279</v>
-      </c>
-      <c r="B163">
-        <v>2038</v>
-      </c>
-      <c r="C163" t="s">
-        <v>281</v>
-      </c>
-      <c r="D163" t="s">
-        <v>282</v>
-      </c>
-      <c r="E163" t="s">
-        <v>14</v>
-      </c>
-      <c r="F163">
-        <v>8.0698099999999897</v>
-      </c>
-      <c r="G163">
-        <v>80520.040000000008</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>283</v>
-      </c>
-      <c r="B164">
-        <v>2036</v>
-      </c>
-      <c r="C164" t="s">
-        <v>8</v>
-      </c>
-      <c r="D164" t="s">
-        <v>284</v>
-      </c>
-      <c r="E164" t="s">
-        <v>10</v>
-      </c>
-      <c r="F164">
-        <v>5.4219599999999986</v>
-      </c>
-      <c r="G164">
-        <v>37831.449999999997</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>283</v>
-      </c>
-      <c r="B165">
-        <v>2047</v>
-      </c>
-      <c r="C165" t="s">
-        <v>284</v>
-      </c>
-      <c r="D165" t="s">
-        <v>285</v>
-      </c>
-      <c r="E165" t="s">
-        <v>286</v>
-      </c>
-      <c r="F165">
-        <v>8.2250380000000014</v>
-      </c>
-      <c r="G165">
-        <v>374918.95</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
-        <v>287</v>
-      </c>
-      <c r="B166">
-        <v>2028</v>
-      </c>
-      <c r="C166" t="s">
-        <v>8</v>
-      </c>
-      <c r="D166" t="s">
-        <v>288</v>
-      </c>
-      <c r="E166" t="s">
-        <v>41</v>
-      </c>
-      <c r="F166">
-        <v>10.524590706516619</v>
-      </c>
-      <c r="G166">
-        <v>21250</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>287</v>
-      </c>
-      <c r="B167">
-        <v>2029</v>
-      </c>
-      <c r="C167" t="s">
-        <v>288</v>
-      </c>
-      <c r="D167" t="s">
-        <v>289</v>
-      </c>
-      <c r="E167" t="s">
-        <v>10</v>
-      </c>
-      <c r="F167">
-        <v>40.350659988379192</v>
-      </c>
-      <c r="G167">
-        <v>48034.200000000012</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>287</v>
-      </c>
-      <c r="B168">
-        <v>2043</v>
-      </c>
-      <c r="C168" t="s">
-        <v>289</v>
-      </c>
-      <c r="D168" t="s">
-        <v>290</v>
-      </c>
-      <c r="E168" t="s">
-        <v>64</v>
-      </c>
-      <c r="F168">
-        <v>3.9527877778783491</v>
-      </c>
-      <c r="G168">
         <v>216153.9</v>
       </c>
     </row>
@@ -5153,28 +4951,30 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="58.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="69.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="32.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="36.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="69.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="38" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="59.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="47.08984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="47.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="40.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="41.36328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="46.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="69.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="69.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="45.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="46" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="69.90625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="46.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="47.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="59.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="38" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="42.90625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="47.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.35">
@@ -5264,13 +5064,13 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="s">
+      <c r="O2" t="s">
         <v>11</v>
       </c>
-      <c r="S2" t="s">
+      <c r="P2" t="s">
         <v>13</v>
       </c>
-      <c r="U2" t="s">
+      <c r="T2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -5278,10 +5078,10 @@
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U3" t="s">
+      <c r="S3" t="s">
         <v>18</v>
       </c>
-      <c r="V3" t="s">
+      <c r="Z3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5289,10 +5089,10 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="R4" t="s">
+      <c r="W4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -5300,817 +5100,793 @@
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+      <c r="S5" t="s">
         <v>28</v>
-      </c>
-      <c r="V5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
         <v>32</v>
-      </c>
-      <c r="M6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z7" t="s">
         <v>35</v>
-      </c>
-      <c r="N7" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" t="s">
         <v>39</v>
-      </c>
-      <c r="N8" t="s">
-        <v>40</v>
-      </c>
-      <c r="P8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y9" t="s">
         <v>44</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" t="s">
-        <v>46</v>
-      </c>
-      <c r="W9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" t="s">
+        <v>48</v>
+      </c>
+      <c r="W11" t="s">
+        <v>50</v>
+      </c>
+      <c r="X11" t="s">
         <v>51</v>
-      </c>
-      <c r="R11" t="s">
-        <v>52</v>
-      </c>
-      <c r="X11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" t="s">
         <v>57</v>
-      </c>
-      <c r="N12" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="R13" t="s">
-        <v>63</v>
+      <c r="V13" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>66</v>
-      </c>
-      <c r="X14" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="R14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" t="s">
         <v>68</v>
       </c>
-      <c r="C15" t="s">
+      <c r="Y15" t="s">
         <v>69</v>
-      </c>
-      <c r="L15" t="s">
-        <v>70</v>
-      </c>
-      <c r="V15" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U16" t="s">
+        <v>71</v>
+      </c>
+      <c r="X16" t="s">
         <v>72</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="O17" t="s">
         <v>75</v>
       </c>
-      <c r="E17" t="s">
+      <c r="Z17" t="s">
         <v>76</v>
-      </c>
-      <c r="J17" t="s">
-        <v>77</v>
-      </c>
-      <c r="X17" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
         <v>80</v>
       </c>
-      <c r="D18" t="s">
+      <c r="M18" t="s">
         <v>81</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>82</v>
-      </c>
-      <c r="P18" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>84</v>
+      </c>
+      <c r="T19" t="s">
         <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="R19" t="s">
-        <v>87</v>
-      </c>
-      <c r="W19" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="X20" t="s">
         <v>89</v>
       </c>
-      <c r="F20" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q20" t="s">
+      <c r="Y20" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s">
         <v>93</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>94</v>
       </c>
-      <c r="Q21" t="s">
-        <v>96</v>
+      <c r="U21" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" t="s">
         <v>97</v>
       </c>
-      <c r="I22" t="s">
+      <c r="Z22" t="s">
         <v>98</v>
-      </c>
-      <c r="R22" t="s">
-        <v>99</v>
-      </c>
-      <c r="V22" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="N23" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="M23" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" t="s">
+        <v>103</v>
+      </c>
+      <c r="T24" t="s">
         <v>105</v>
-      </c>
-      <c r="V24" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" t="s">
-        <v>113</v>
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>116</v>
+      </c>
+      <c r="X28" t="s">
         <v>118</v>
-      </c>
-      <c r="B28" t="s">
-        <v>119</v>
-      </c>
-      <c r="W28" t="s">
-        <v>121</v>
-      </c>
-      <c r="X28" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" t="s">
-        <v>124</v>
-      </c>
-      <c r="H29" t="s">
-        <v>125</v>
+        <v>119</v>
+      </c>
+      <c r="C29" t="s">
+        <v>120</v>
+      </c>
+      <c r="K29" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B30" t="s">
-        <v>128</v>
-      </c>
-      <c r="G30" t="s">
-        <v>129</v>
-      </c>
-      <c r="L30" t="s">
-        <v>130</v>
+        <v>123</v>
+      </c>
+      <c r="E30" t="s">
+        <v>124</v>
+      </c>
+      <c r="N30" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" t="s">
-        <v>132</v>
-      </c>
-      <c r="G31" t="s">
-        <v>133</v>
-      </c>
-      <c r="J31" t="s">
-        <v>135</v>
-      </c>
-      <c r="P31" t="s">
-        <v>136</v>
+        <v>127</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="O31" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G32" t="s">
-        <v>138</v>
-      </c>
-      <c r="R32" t="s">
-        <v>140</v>
+        <v>131</v>
+      </c>
+      <c r="H32" t="s">
+        <v>132</v>
+      </c>
+      <c r="S32" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" t="s">
-        <v>142</v>
+        <v>135</v>
+      </c>
+      <c r="F33" t="s">
+        <v>136</v>
       </c>
       <c r="J33" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F34" t="s">
-        <v>145</v>
-      </c>
-      <c r="L34" t="s">
-        <v>146</v>
+        <v>139</v>
+      </c>
+      <c r="E34" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" t="s">
-        <v>148</v>
-      </c>
-      <c r="O35" t="s">
-        <v>149</v>
-      </c>
-      <c r="P35" t="s">
-        <v>151</v>
+        <v>142</v>
+      </c>
+      <c r="K35" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>144</v>
+      </c>
+      <c r="W35" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F36" t="s">
-        <v>153</v>
-      </c>
-      <c r="M36" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>155</v>
+        <v>147</v>
+      </c>
+      <c r="L36" t="s">
+        <v>148</v>
+      </c>
+      <c r="O36" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" t="s">
-        <v>157</v>
-      </c>
-      <c r="U37" t="s">
-        <v>159</v>
+        <v>151</v>
+      </c>
+      <c r="B37" t="s">
+        <v>152</v>
+      </c>
+      <c r="C37" t="s">
+        <v>153</v>
+      </c>
+      <c r="V37" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
-      </c>
-      <c r="L38" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>164</v>
+        <v>157</v>
+      </c>
+      <c r="I38" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C39" t="s">
-        <v>166</v>
-      </c>
-      <c r="P39" t="s">
-        <v>167</v>
+        <v>160</v>
+      </c>
+      <c r="F39" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F40" t="s">
-        <v>169</v>
-      </c>
-      <c r="M40" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>171</v>
+        <v>163</v>
+      </c>
+      <c r="C40" t="s">
+        <v>164</v>
+      </c>
+      <c r="G40" t="s">
+        <v>165</v>
+      </c>
+      <c r="W40" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B41" t="s">
-        <v>173</v>
-      </c>
-      <c r="K41" t="s">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="D41" t="s">
+        <v>169</v>
+      </c>
+      <c r="P41" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F42" t="s">
-        <v>177</v>
-      </c>
-      <c r="I42" t="s">
-        <v>178</v>
+        <v>172</v>
+      </c>
+      <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V43" t="s">
-        <v>183</v>
-      </c>
-      <c r="X43" t="s">
-        <v>184</v>
+        <v>177</v>
+      </c>
+      <c r="T43" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E44" t="s">
-        <v>186</v>
-      </c>
-      <c r="S44" t="s">
-        <v>187</v>
-      </c>
-      <c r="X44" t="s">
-        <v>188</v>
+        <v>180</v>
+      </c>
+      <c r="C44" t="s">
+        <v>181</v>
+      </c>
+      <c r="R44" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>190</v>
+        <v>183</v>
+      </c>
+      <c r="U45" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C46" t="s">
-        <v>192</v>
-      </c>
-      <c r="V46" t="s">
-        <v>193</v>
-      </c>
-      <c r="W46" t="s">
-        <v>194</v>
+        <v>185</v>
+      </c>
+      <c r="E46" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B47" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>198</v>
+        <v>189</v>
+      </c>
+      <c r="C47" t="s">
+        <v>190</v>
+      </c>
+      <c r="S47" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>200</v>
-      </c>
-      <c r="K48" t="s">
-        <v>201</v>
+        <v>193</v>
+      </c>
+      <c r="H48" t="s">
+        <v>194</v>
+      </c>
+      <c r="J48" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E49" t="s">
-        <v>204</v>
-      </c>
-      <c r="I49" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="B49" t="s">
+        <v>197</v>
+      </c>
+      <c r="H49" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D50" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F50" t="s">
-        <v>208</v>
-      </c>
-      <c r="K50" t="s">
-        <v>209</v>
+        <v>201</v>
+      </c>
+      <c r="L50" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="P51" t="s">
-        <v>211</v>
-      </c>
-      <c r="T51" t="s">
-        <v>212</v>
+        <v>203</v>
+      </c>
+      <c r="O51" t="s">
+        <v>204</v>
+      </c>
+      <c r="X51" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B52" t="s">
-        <v>215</v>
-      </c>
-      <c r="G52" t="s">
-        <v>216</v>
-      </c>
-      <c r="O52" t="s">
-        <v>217</v>
+        <v>206</v>
+      </c>
+      <c r="C52" t="s">
+        <v>207</v>
+      </c>
+      <c r="J52" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F53" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>220</v>
+        <v>210</v>
+      </c>
+      <c r="C53" t="s">
+        <v>211</v>
+      </c>
+      <c r="N53" t="s">
+        <v>212</v>
+      </c>
+      <c r="R53" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>224</v>
+        <v>214</v>
+      </c>
+      <c r="U54" t="s">
+        <v>215</v>
+      </c>
+      <c r="X54" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="S55" t="s">
-        <v>226</v>
+        <v>218</v>
+      </c>
+      <c r="X55" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="K56" t="s">
-        <v>229</v>
-      </c>
-      <c r="U56" t="s">
-        <v>230</v>
+        <v>222</v>
+      </c>
+      <c r="M56" t="s">
+        <v>223</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="K57" t="s">
-        <v>232</v>
-      </c>
-      <c r="W57" t="s">
-        <v>233</v>
-      </c>
-      <c r="X57" t="s">
-        <v>234</v>
+        <v>225</v>
+      </c>
+      <c r="M57" t="s">
+        <v>226</v>
+      </c>
+      <c r="P57" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="I58" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>237</v>
+        <v>229</v>
+      </c>
+      <c r="M58" t="s">
+        <v>230</v>
+      </c>
+      <c r="V58" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C59" t="s">
-        <v>239</v>
-      </c>
-      <c r="R59" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>242</v>
+        <v>233</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="S60" t="s">
-        <v>244</v>
-      </c>
-      <c r="T60" t="s">
-        <v>245</v>
+        <v>236</v>
+      </c>
+      <c r="U60" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F61" t="s">
-        <v>247</v>
-      </c>
-      <c r="J61" t="s">
-        <v>248</v>
+        <v>239</v>
+      </c>
+      <c r="D61" t="s">
+        <v>240</v>
+      </c>
+      <c r="N61" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="N62" t="s">
-        <v>251</v>
-      </c>
-      <c r="X62" t="s">
-        <v>252</v>
+        <v>243</v>
+      </c>
+      <c r="P62" t="s">
+        <v>244</v>
+      </c>
+      <c r="R62" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E63" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M63" t="s">
-        <v>256</v>
+        <v>249</v>
+      </c>
+      <c r="P63" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="H64" t="s">
-        <v>259</v>
+        <v>252</v>
+      </c>
+      <c r="L64" t="s">
+        <v>253</v>
+      </c>
+      <c r="P64" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B65" t="s">
-        <v>262</v>
+        <v>256</v>
+      </c>
+      <c r="C65" t="s">
+        <v>257</v>
       </c>
       <c r="E65" t="s">
-        <v>263</v>
-      </c>
-      <c r="J65" t="s">
-        <v>264</v>
+        <v>258</v>
+      </c>
+      <c r="O65" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C66" t="s">
-        <v>266</v>
-      </c>
-      <c r="I66" t="s">
-        <v>267</v>
+        <v>260</v>
+      </c>
+      <c r="F66" t="s">
+        <v>261</v>
+      </c>
+      <c r="L66" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F67" t="s">
-        <v>269</v>
+        <v>263</v>
+      </c>
+      <c r="D67" t="s">
+        <v>264</v>
       </c>
       <c r="P67" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>271</v>
+        <v>265</v>
+      </c>
+      <c r="V67" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F68" t="s">
-        <v>273</v>
-      </c>
-      <c r="H68" t="s">
-        <v>274</v>
+        <v>267</v>
+      </c>
+      <c r="D68" t="s">
+        <v>268</v>
+      </c>
+      <c r="G68" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D69" t="s">
-        <v>276</v>
-      </c>
-      <c r="P69" t="s">
-        <v>277</v>
-      </c>
-      <c r="U69" t="s">
-        <v>278</v>
+        <v>270</v>
+      </c>
+      <c r="C69" t="s">
+        <v>271</v>
+      </c>
+      <c r="O69" t="s">
+        <v>272</v>
+      </c>
+      <c r="S69" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C70" t="s">
-        <v>280</v>
-      </c>
-      <c r="M70" t="s">
-        <v>281</v>
-      </c>
-      <c r="N70" t="s">
-        <v>282</v>
+        <v>274</v>
+      </c>
+      <c r="E70" t="s">
+        <v>275</v>
+      </c>
+      <c r="L70" t="s">
+        <v>276</v>
+      </c>
+      <c r="O70" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="L71" t="s">
-        <v>284</v>
+        <v>278</v>
+      </c>
+      <c r="K71" t="s">
+        <v>279</v>
       </c>
       <c r="W71" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
+      </c>
+      <c r="B72" t="s">
+        <v>282</v>
       </c>
       <c r="D72" t="s">
-        <v>288</v>
-      </c>
-      <c r="E72" t="s">
-        <v>289</v>
-      </c>
-      <c r="S72" t="s">
-        <v>290</v>
+        <v>283</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -6124,31 +5900,31 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="58.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="78.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="78.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="49.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="70.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="71.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="44.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="80.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="42.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="69.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="41.6328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="71.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="49.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="47.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="45.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="71.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="68.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="54.6328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="42.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="48.36328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="55.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.6328125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="50.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="54.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="31.7265625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="51.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="48.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="56.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.35">
@@ -6238,13 +6014,13 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="O2" t="s">
         <v>12</v>
       </c>
-      <c r="S2" t="s">
+      <c r="P2" t="s">
         <v>14</v>
       </c>
-      <c r="U2" t="s">
+      <c r="T2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6252,10 +6028,10 @@
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="S3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6263,10 +6039,10 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H4" t="s">
         <v>10</v>
       </c>
-      <c r="R4" t="s">
+      <c r="W4" t="s">
         <v>24</v>
       </c>
     </row>
@@ -6274,817 +6050,793 @@
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="V5" t="s">
-        <v>14</v>
+      <c r="S5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="G6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N8" t="s">
-        <v>41</v>
-      </c>
-      <c r="P8" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="O8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="M9" t="s">
+      <c r="P9" t="s">
         <v>12</v>
       </c>
-      <c r="W9" t="s">
-        <v>48</v>
+      <c r="Y9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" t="s">
-        <v>16</v>
+        <v>45</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="R11" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="P11" t="s">
+        <v>49</v>
+      </c>
+      <c r="W11" t="s">
+        <v>12</v>
       </c>
       <c r="X11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" t="s">
         <v>56</v>
       </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
       <c r="N12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="R13" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="V13" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>10</v>
-      </c>
-      <c r="X14" t="s">
-        <v>16</v>
+        <v>63</v>
+      </c>
+      <c r="R14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" t="s">
-        <v>33</v>
-      </c>
-      <c r="V15" t="s">
-        <v>41</v>
+        <v>67</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>16</v>
-      </c>
-      <c r="V16" t="s">
+        <v>70</v>
+      </c>
+      <c r="U16" t="s">
         <v>10</v>
+      </c>
+      <c r="X16" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="J17" t="s">
+      <c r="O17" t="s">
         <v>12</v>
       </c>
-      <c r="X17" t="s">
-        <v>79</v>
+      <c r="Z17" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
-      </c>
-      <c r="O18" t="s">
+        <v>14</v>
+      </c>
+      <c r="M18" t="s">
         <v>10</v>
       </c>
       <c r="P18" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R19" t="s">
-        <v>64</v>
-      </c>
-      <c r="W19" t="s">
-        <v>53</v>
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>67</v>
+      </c>
+      <c r="T19" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F20" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>92</v>
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="X20" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I21" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>41</v>
+        <v>92</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" t="s">
+        <v>58</v>
+      </c>
+      <c r="U21" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I22" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" t="s">
         <v>10</v>
       </c>
-      <c r="R22" t="s">
-        <v>14</v>
-      </c>
-      <c r="V22" t="s">
-        <v>101</v>
+      <c r="Z22" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="N23" t="s">
-        <v>14</v>
+        <v>100</v>
+      </c>
+      <c r="M23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" t="s">
         <v>104</v>
       </c>
-      <c r="D24" t="s">
-        <v>106</v>
-      </c>
-      <c r="V24" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>41</v>
+      <c r="T24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" t="s">
-        <v>114</v>
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" t="s">
-        <v>117</v>
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B28" t="s">
-        <v>120</v>
-      </c>
-      <c r="W28" t="s">
-        <v>14</v>
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>117</v>
       </c>
       <c r="X28" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" t="s">
-        <v>126</v>
+        <v>119</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="K29" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B30" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" t="s">
         <v>10</v>
       </c>
-      <c r="G30" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" t="s">
-        <v>79</v>
+      <c r="N30" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="G31" t="s">
-        <v>134</v>
-      </c>
-      <c r="J31" t="s">
-        <v>16</v>
-      </c>
-      <c r="P31" t="s">
-        <v>41</v>
+      <c r="O31" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G32" t="s">
-        <v>139</v>
-      </c>
-      <c r="R32" t="s">
-        <v>14</v>
+        <v>131</v>
+      </c>
+      <c r="H32" t="s">
+        <v>133</v>
+      </c>
+      <c r="S32" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" t="s">
-        <v>53</v>
+        <v>135</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F34" t="s">
-        <v>106</v>
-      </c>
-      <c r="L34" t="s">
-        <v>41</v>
+        <v>139</v>
+      </c>
+      <c r="E34" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" t="s">
-        <v>27</v>
-      </c>
-      <c r="O35" t="s">
-        <v>150</v>
-      </c>
-      <c r="P35" t="s">
-        <v>48</v>
+        <v>142</v>
+      </c>
+      <c r="K35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>86</v>
+      </c>
+      <c r="W35" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
-      </c>
-      <c r="M36" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>14</v>
+        <v>49</v>
+      </c>
+      <c r="L36" t="s">
+        <v>149</v>
+      </c>
+      <c r="O36" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" t="s">
-        <v>158</v>
-      </c>
-      <c r="U37" t="s">
-        <v>64</v>
+        <v>151</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>154</v>
+      </c>
+      <c r="V37" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D38" t="s">
-        <v>53</v>
-      </c>
-      <c r="L38" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>79</v>
+        <v>49</v>
+      </c>
+      <c r="I38" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F39" t="s">
         <v>10</v>
       </c>
-      <c r="P39" t="s">
-        <v>79</v>
+      <c r="J39" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F40" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" t="s">
         <v>10</v>
       </c>
-      <c r="M40" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>14</v>
+      <c r="G40" t="s">
+        <v>166</v>
+      </c>
+      <c r="W40" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K41" t="s">
-        <v>175</v>
+        <v>168</v>
+      </c>
+      <c r="D41" t="s">
+        <v>49</v>
+      </c>
+      <c r="P41" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F42" t="s">
-        <v>53</v>
-      </c>
-      <c r="I42" t="s">
-        <v>179</v>
+        <v>172</v>
+      </c>
+      <c r="D42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F43" t="s">
-        <v>182</v>
-      </c>
-      <c r="V43" t="s">
-        <v>53</v>
-      </c>
-      <c r="X43" t="s">
-        <v>64</v>
+        <v>178</v>
+      </c>
+      <c r="T43" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E44" t="s">
-        <v>27</v>
-      </c>
-      <c r="S44" t="s">
-        <v>14</v>
-      </c>
-      <c r="X44" t="s">
-        <v>41</v>
+        <v>180</v>
+      </c>
+      <c r="C44" t="s">
+        <v>67</v>
+      </c>
+      <c r="R44" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>64</v>
+        <v>183</v>
+      </c>
+      <c r="U45" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C46" t="s">
-        <v>41</v>
-      </c>
-      <c r="V46" t="s">
-        <v>27</v>
-      </c>
-      <c r="W46" t="s">
-        <v>14</v>
+        <v>185</v>
+      </c>
+      <c r="E46" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B47" t="s">
+        <v>189</v>
+      </c>
+      <c r="C47" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>41</v>
+      <c r="S47" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
-      <c r="K48" t="s">
-        <v>202</v>
+      <c r="H48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J48" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E49" t="s">
-        <v>41</v>
-      </c>
-      <c r="I49" t="s">
-        <v>106</v>
+        <v>196</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="H49" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
-      </c>
-      <c r="K50" t="s">
-        <v>101</v>
+        <v>67</v>
+      </c>
+      <c r="L50" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="P51" t="s">
+        <v>203</v>
+      </c>
+      <c r="O51" t="s">
         <v>10</v>
       </c>
-      <c r="T51" t="s">
-        <v>213</v>
+      <c r="X51" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C52" t="s">
         <v>10</v>
       </c>
-      <c r="G52" t="s">
-        <v>12</v>
-      </c>
-      <c r="O52" t="s">
-        <v>48</v>
+      <c r="J52" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" t="s">
         <v>10</v>
       </c>
-      <c r="Z53" t="s">
-        <v>221</v>
+      <c r="N53" t="s">
+        <v>56</v>
+      </c>
+      <c r="R53" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>64</v>
+        <v>214</v>
+      </c>
+      <c r="U54" t="s">
+        <v>10</v>
+      </c>
+      <c r="X54" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="S55" t="s">
-        <v>227</v>
+        <v>218</v>
+      </c>
+      <c r="X55" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="K56" t="s">
-        <v>139</v>
-      </c>
-      <c r="U56" t="s">
-        <v>101</v>
+        <v>222</v>
+      </c>
+      <c r="M56" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="K57" t="s">
-        <v>10</v>
-      </c>
-      <c r="W57" t="s">
-        <v>213</v>
-      </c>
-      <c r="X57" t="s">
-        <v>12</v>
+        <v>225</v>
+      </c>
+      <c r="M57" t="s">
+        <v>14</v>
+      </c>
+      <c r="P57" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="I58" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>14</v>
+        <v>229</v>
+      </c>
+      <c r="M58" t="s">
+        <v>114</v>
+      </c>
+      <c r="V58" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
-      </c>
-      <c r="R59" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>41</v>
+        <v>67</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="S60" t="s">
-        <v>16</v>
-      </c>
-      <c r="T60" t="s">
-        <v>150</v>
+        <v>236</v>
+      </c>
+      <c r="U60" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F61" t="s">
-        <v>41</v>
-      </c>
-      <c r="J61" t="s">
-        <v>249</v>
+        <v>239</v>
+      </c>
+      <c r="D61" t="s">
+        <v>56</v>
+      </c>
+      <c r="N61" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="N62" t="s">
-        <v>41</v>
-      </c>
-      <c r="X62" t="s">
-        <v>253</v>
+        <v>243</v>
+      </c>
+      <c r="P62" t="s">
+        <v>56</v>
+      </c>
+      <c r="R62" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="M63" t="s">
-        <v>257</v>
+        <v>250</v>
+      </c>
+      <c r="P63" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="H64" t="s">
-        <v>260</v>
+        <v>252</v>
+      </c>
+      <c r="L64" t="s">
+        <v>254</v>
+      </c>
+      <c r="P64" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B65" t="s">
+        <v>256</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
         <v>10</v>
       </c>
-      <c r="E65" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" t="s">
-        <v>64</v>
+      <c r="O65" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C66" t="s">
-        <v>33</v>
-      </c>
-      <c r="I66" t="s">
-        <v>41</v>
+        <v>260</v>
+      </c>
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+      <c r="L66" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F67" t="s">
-        <v>16</v>
+        <v>263</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
       </c>
       <c r="P67" t="s">
         <v>10</v>
       </c>
-      <c r="Y67" t="s">
-        <v>64</v>
+      <c r="V67" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F68" t="s">
-        <v>37</v>
-      </c>
-      <c r="H68" t="s">
-        <v>14</v>
+        <v>267</v>
+      </c>
+      <c r="D68" t="s">
+        <v>40</v>
+      </c>
+      <c r="G68" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D69" t="s">
-        <v>139</v>
-      </c>
-      <c r="P69" t="s">
+        <v>270</v>
+      </c>
+      <c r="C69" t="s">
+        <v>133</v>
+      </c>
+      <c r="O69" t="s">
         <v>12</v>
       </c>
-      <c r="U69" t="s">
-        <v>14</v>
+      <c r="S69" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C70" t="s">
+        <v>274</v>
+      </c>
+      <c r="E70" t="s">
         <v>10</v>
       </c>
-      <c r="M70" t="s">
+      <c r="L70" t="s">
         <v>12</v>
       </c>
-      <c r="N70" t="s">
-        <v>14</v>
+      <c r="O70" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="L71" t="s">
+        <v>278</v>
+      </c>
+      <c r="K71" t="s">
         <v>10</v>
       </c>
       <c r="W71" t="s">
-        <v>286</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
+      </c>
+      <c r="B72" t="s">
+        <v>56</v>
       </c>
       <c r="D72" t="s">
-        <v>41</v>
-      </c>
-      <c r="E72" t="s">
         <v>10</v>
       </c>
-      <c r="S72" t="s">
-        <v>64</v>
+      <c r="Y72" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -7108,13 +6860,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -7122,13 +6874,13 @@
         <v>2026</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>1193.590151684793</v>
+        <v>974.37770354478232</v>
       </c>
       <c r="D2">
-        <v>1999453.8870892399</v>
+        <v>1998051.748586386</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -7136,13 +6888,13 @@
         <v>2027</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>1210.0297574794261</v>
+        <v>1084.581013280236</v>
       </c>
       <c r="D3">
-        <v>1998108.8686661471</v>
+        <v>1998327.9923664711</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -7150,13 +6902,13 @@
         <v>2028</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>812.63635875349405</v>
+        <v>1152.3366562593701</v>
       </c>
       <c r="D4">
-        <v>1997717.4663213801</v>
+        <v>1998187.723270868</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -7167,10 +6919,10 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>942.24478552106007</v>
+        <v>1332.561765714878</v>
       </c>
       <c r="D5">
-        <v>1999798.15585376</v>
+        <v>1998798.4922136359</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -7178,13 +6930,13 @@
         <v>2030</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>1409.0495285757511</v>
+        <v>1009.258842363208</v>
       </c>
       <c r="D6">
-        <v>1999115.3318635901</v>
+        <v>1999643.0699914419</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -7192,13 +6944,13 @@
         <v>2031</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>259.87643874109301</v>
+        <v>333.20193027850678</v>
       </c>
       <c r="D7">
-        <v>1991319.3489999999</v>
+        <v>1998163.15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -7206,13 +6958,13 @@
         <v>2032</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>259.56992570738112</v>
+        <v>338.02323570634849</v>
       </c>
       <c r="D8">
-        <v>1996163.741999507</v>
+        <v>1998130.343757181</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -7220,13 +6972,13 @@
         <v>2033</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>281.40750294044852</v>
+        <v>253.96955762647971</v>
       </c>
       <c r="D9">
-        <v>1999156.7518223419</v>
+        <v>1994397.645</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -7237,10 +6989,10 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>301.19234349675378</v>
+        <v>295.29705624898452</v>
       </c>
       <c r="D10">
-        <v>1999625.7043016921</v>
+        <v>1997482.3148123799</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -7248,13 +7000,13 @@
         <v>2035</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>284.67662467863232</v>
+        <v>270.54061881453038</v>
       </c>
       <c r="D11">
-        <v>1993592.4710972901</v>
+        <v>1997096.812531349</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -7262,13 +7014,13 @@
         <v>2036</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>283.56893371046817</v>
+        <v>252.4832984422172</v>
       </c>
       <c r="D12">
-        <v>1997277.7990000001</v>
+        <v>1994054.0405821139</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -7279,10 +7031,10 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>384.88978997376529</v>
+        <v>397.522392032472</v>
       </c>
       <c r="D13">
-        <v>1998565.5888692059</v>
+        <v>1997573.847657105</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -7290,13 +7042,13 @@
         <v>2038</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>387.30638764141941</v>
+        <v>221.90168739693189</v>
       </c>
       <c r="D14">
-        <v>1998732.6708655171</v>
+        <v>1997323.5463978399</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -7304,13 +7056,13 @@
         <v>2039</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>116.2640099839913</v>
+        <v>281.11412547330332</v>
       </c>
       <c r="D15">
-        <v>1996285.7707661351</v>
+        <v>1998655.3731545701</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -7318,13 +7070,13 @@
         <v>2040</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>258.29461866717679</v>
+        <v>205.10219600082331</v>
       </c>
       <c r="D16">
-        <v>1997161.4712029111</v>
+        <v>1998311.4553570589</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -7332,13 +7084,13 @@
         <v>2041</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>46.372698661254972</v>
+        <v>106.229531584965</v>
       </c>
       <c r="D17">
-        <v>1820320.0400925579</v>
+        <v>1977043.6665000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -7346,13 +7098,13 @@
         <v>2042</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>35.675085776424922</v>
+        <v>47.059263752941312</v>
       </c>
       <c r="D18">
-        <v>1954513.1247394241</v>
+        <v>1966054.3374892659</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -7363,10 +7115,10 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>42.448802613828967</v>
+        <v>47.821246212379357</v>
       </c>
       <c r="D19">
-        <v>1925493.8808112061</v>
+        <v>1930456.905631053</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -7374,13 +7126,13 @@
         <v>2044</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20">
-        <v>8.7682398125150183</v>
+        <v>19.70135806621921</v>
       </c>
       <c r="D20">
-        <v>1215744.8186444291</v>
+        <v>1969599.3847459999</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -7391,10 +7143,10 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>121.3475799348702</v>
+        <v>27.428315038448979</v>
       </c>
       <c r="D21">
-        <v>1896880.334314235</v>
+        <v>1849514.1682884321</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -7402,13 +7154,13 @@
         <v>2046</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>-74.194602026131065</v>
+        <v>114.5598359622544</v>
       </c>
       <c r="D22">
-        <v>1777992.058270647</v>
+        <v>1828343.8095022771</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -7416,13 +7168,13 @@
         <v>2047</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>57.898578018123089</v>
+        <v>84.675843494946903</v>
       </c>
       <c r="D23">
-        <v>1893461.260412965</v>
+        <v>1718349.2241290391</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -7430,13 +7182,13 @@
         <v>2048</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24">
-        <v>58.674914240902467</v>
+        <v>-6.8420666748929904</v>
       </c>
       <c r="D24">
-        <v>1762451.4486447929</v>
+        <v>1596391.173170354</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -7444,13 +7196,13 @@
         <v>2049</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>89.75956530141454</v>
+        <v>78.778845468870728</v>
       </c>
       <c r="D25">
-        <v>1953429.747128933</v>
+        <v>1068476.166736667</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -7458,13 +7210,13 @@
         <v>2050</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>201.97933419005921</v>
+        <v>51.643101989711063</v>
       </c>
       <c r="D26">
-        <v>1660968.0197912201</v>
+        <v>1954903.369697636</v>
       </c>
     </row>
   </sheetData>

--- a/plan_renovation_solution.xlsx
+++ b/plan_renovation_solution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youss\Desktop\Projet ST7\sia_efficacity_projet_st7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867EFD72-06DF-473F-8C7B-D08B706AB1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F36A43F-F624-4907-AA9B-57CD41EF91A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="transitions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="302">
   <si>
     <t>building</t>
   </si>
@@ -955,10 +955,16 @@
     <t>Consommation_init</t>
   </si>
   <si>
-    <t>Pourcentage</t>
-  </si>
-  <si>
     <t>Nbr renov moyennes par an</t>
+  </si>
+  <si>
+    <t>disponibilité (%)</t>
+  </si>
+  <si>
+    <t>Disponibilité min</t>
+  </si>
+  <si>
+    <t>Gains cumulé (en %)</t>
   </si>
 </sst>
 </file>
@@ -1036,19 +1042,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1355,6 +1364,313 @@
         <c:axId val="1157331312"/>
         <c:axId val="1157332272"/>
       </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Nbr de rénovations moyen par an</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="23"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="C00000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="fr-FR"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-7181-4AB7-89B6-E882280F6BAD}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>stats_annees!$A$2:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>stats_annees!$H$2:$H$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.36</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7181-4AB7-89B6-E882280F6BAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1157331312"/>
+        <c:axId val="1157332272"/>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="1157331312"/>
         <c:scaling>
@@ -1470,6 +1786,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1508,456 +1855,6 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>stats_annees!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>gain_cumulé</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>stats_annees!$A$2:$A$26</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>2026</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2027</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2028</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2029</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2030</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2031</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2032</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2033</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2034</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2035</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2036</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2037</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2038</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2039</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2040</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2041</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2042</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2043</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2044</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2045</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2046</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2047</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2048</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2049</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2050</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>stats_annees!$E$2:$E$26</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>974.37770354478232</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2058.9587168250182</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3211.2953730843883</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4543.8571387992661</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5553.1159811624739</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5886.3179114409804</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6224.3411471473291</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6478.3107047738085</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>6773.6077610227931</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7044.1483798373238</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7296.6316782795411</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7694.1540703120136</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>7916.0557577089457</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8197.1698831822487</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8402.2720791830725</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>8508.5016107680367</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8555.5608745209774</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8603.3821207333567</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8623.0834787995755</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8650.5117938380245</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8765.071629800279</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8849.7474732952251</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8842.9054066203316</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>8921.6842520892023</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8973.3273540789141</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B975-4DF9-A9FB-F565C657CA47}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1158837280"/>
-        <c:axId val="1158841120"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1158837280"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1158841120"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1158841120"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1158837280"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2035,7 +1932,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-MA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2054,7 +1951,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Pourcentage</c:v>
+                  <c:v>Gains cumulé (en %)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2083,6 +1980,199 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-469B-4101-940A-CCE820CD3574}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-469B-4101-940A-CCE820CD3574}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="24"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-469B-4101-940A-CCE820CD3574}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.11404409062376664"/>
+                  <c:y val="-0.14632559954656538"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-469B-4101-940A-CCE820CD3574}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.10291783787998462"/>
+                  <c:y val="-0.11328433513282479"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-469B-4101-940A-CCE820CD3574}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="24"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-7.7369136067855088E-2"/>
+                  <c:y val="0.1284443327356245"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-469B-4101-940A-CCE820CD3574}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>stats_annees!$A$2:$A$26</c:f>
@@ -2447,7 +2537,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2462,6 +2552,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-MA"/>
+              <a:t>budget par année</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2861,6 +2976,676 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-MA"/>
+              <a:t>Rénovations réalisées Administration</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Nombre de bâtiments rénovés</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>availability_by_category!$B$2:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>availability_by_category!$C$2:$C$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-63BC-48E5-9707-E41C06E64B09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="155930912"/>
+        <c:axId val="155924672"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>20% de la catégorie</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>availability_by_category!$B$2:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>availability_by_category!$D$2:$D$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-63BC-48E5-9707-E41C06E64B09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="155930912"/>
+        <c:axId val="155924672"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="155930912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="155924672"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="155924672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="155930912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -2896,13 +3681,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="fr-MA"/>
-              <a:t>Occupation</a:t>
+              <a:t>Disponiblité Autres</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="fr-MA" baseline="0"/>
-              <a:t> Administration</a:t>
-            </a:r>
-            <a:endParaRPr lang="fr-MA"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -2938,207 +3718,197 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Nombre de bâtiments rénovés</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:strRef>
-              <c:f>availability_by_category!$A$2:$A$26</c:f>
-              <c:strCache>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Administration</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Administration</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:xVal>
-          <c:yVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
             <c:numRef>
-              <c:f>availability_by_category!$E$2:$E$26</c:f>
+              <c:f>availability_by_category!$B$27:$B$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>2027</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>2028</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2029</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>availability_by_category!$C$27:$C$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.16666666666666671</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CDFC-4BC6-9A90-B1207AE76651}"/>
+              <c16:uniqueId val="{00000004-CC44-4A21-85DD-9142CCA15099}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3150,30 +3920,227 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1240024240"/>
-        <c:axId val="1240024720"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1240024240"/>
+        <c:gapWidth val="219"/>
+        <c:axId val="155926112"/>
+        <c:axId val="155921312"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>20% de la catégorie</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>availability_by_category!$B$27:$B$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>availability_by_category!$D$27:$D$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-CC44-4A21-85DD-9142CCA15099}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="155926112"/>
+        <c:axId val="155921312"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="155926112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3182,8 +4149,8 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -3210,12 +4177,15 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1240024720"/>
+        <c:crossAx val="155921312"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="1240024720"/>
+        <c:axId val="155921312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3241,14 +4211,8 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3272,9 +4236,9 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1240024240"/>
+        <c:crossAx val="155926112"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3284,16 +4248,40 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3363,7 +4351,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="fr-MA"/>
-              <a:t>Occupation Autres</a:t>
+              <a:t>Rénovations</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="fr-MA" baseline="0"/>
+              <a:t> réalisées Enseignement</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3400,207 +4392,197 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Nombre de bâtiments rénovés</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:strRef>
-              <c:f>availability_by_category!$A$27:$A$51</c:f>
-              <c:strCache>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Autres</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Autres</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:xVal>
-          <c:yVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
             <c:numRef>
-              <c:f>availability_by_category!$E$27:$E$51</c:f>
+              <c:f>availability_by_category!$B$52:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>7.6923076923076927E-2</c:v>
+                  <c:v>2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.15384615384615391</c:v>
+                  <c:v>2027</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.19230769230769229</c:v>
+                  <c:v>2028</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1153846153846154</c:v>
+                  <c:v>2029</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.8461538461538457E-2</c:v>
+                  <c:v>2030</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2031</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.6923076923076927E-2</c:v>
+                  <c:v>2032</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>2033</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.6923076923076927E-2</c:v>
+                  <c:v>2034</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.8461538461538457E-2</c:v>
+                  <c:v>2035</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.6923076923076927E-2</c:v>
+                  <c:v>2036</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.15384615384615391</c:v>
+                  <c:v>2037</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.1153846153846154</c:v>
+                  <c:v>2038</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.1153846153846154</c:v>
+                  <c:v>2039</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.19230769230769229</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>2041</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.6923076923076927E-2</c:v>
+                  <c:v>2042</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>2043</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>2044</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.6923076923076927E-2</c:v>
+                  <c:v>2045</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.1153846153846154</c:v>
+                  <c:v>2046</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.8461538461538457E-2</c:v>
+                  <c:v>2047</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1153846153846154</c:v>
+                  <c:v>2048</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.15384615384615391</c:v>
+                  <c:v>2049</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.15384615384615391</c:v>
+                  <c:v>2050</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>availability_by_category!$C$52:$C$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6E8B-4122-AD43-DA0C3087C601}"/>
+              <c16:uniqueId val="{00000000-CA8F-493F-B81A-381E2D02BC9E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3612,30 +4594,228 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1163470480"/>
-        <c:axId val="1163470960"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1163470480"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="155966432"/>
+        <c:axId val="155968832"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>20% de la catégorie</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>availability_by_category!$B$52:$B$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>availability_by_category!$D$52:$D$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CA8F-493F-B81A-381E2D02BC9E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="155966432"/>
+        <c:axId val="155968832"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="155966432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3644,8 +4824,8 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -3672,12 +4852,15 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1163470960"/>
+        <c:crossAx val="155968832"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="1163470960"/>
+        <c:axId val="155968832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3703,14 +4886,8 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3734,9 +4911,9 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1163470480"/>
+        <c:crossAx val="155966432"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3746,16 +4923,40 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3825,8 +5026,13 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="fr-MA"/>
-              <a:t>Occupation Enseignement</a:t>
+              <a:t>Rénovations</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="fr-MA" baseline="0"/>
+              <a:t> réalisées Sports</a:t>
+            </a:r>
+            <a:endParaRPr lang="fr-MA"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3862,207 +5068,197 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Nombre de bâtiments rénovés</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:strRef>
-              <c:f>availability_by_category!$A$52:$A$76</c:f>
-              <c:strCache>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Enseignement</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:xVal>
-          <c:yVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
             <c:numRef>
-              <c:f>availability_by_category!$E$52:$E$76</c:f>
+              <c:f>availability_by_category!$B$77:$B$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>0.10344827586206901</c:v>
+                  <c:v>2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.17241379310344829</c:v>
+                  <c:v>2027</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.17241379310344829</c:v>
+                  <c:v>2028</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.17241379310344829</c:v>
+                  <c:v>2029</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.17241379310344829</c:v>
+                  <c:v>2030</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2031</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.4482758620689648E-2</c:v>
+                  <c:v>2032</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2033</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2034</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2035</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2036</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.4482758620689648E-2</c:v>
+                  <c:v>2037</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.4482758620689648E-2</c:v>
+                  <c:v>2038</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.10344827586206901</c:v>
+                  <c:v>2039</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.10344827586206901</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.4482758620689648E-2</c:v>
+                  <c:v>2041</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>2042</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2043</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2044</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.4482758620689648E-2</c:v>
+                  <c:v>2045</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.4482758620689648E-2</c:v>
+                  <c:v>2046</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2047</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.10344827586206901</c:v>
+                  <c:v>2048</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.4482758620689648E-2</c:v>
+                  <c:v>2049</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.8965517241379309E-2</c:v>
+                  <c:v>2050</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>availability_by_category!$C$77:$C$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FFDD-43DD-B820-8A94F5346317}"/>
+              <c16:uniqueId val="{00000000-C5D5-46C7-8335-F8049FE30E65}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4074,30 +5270,228 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="989048816"/>
-        <c:axId val="1239484912"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="989048816"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="155938112"/>
+        <c:axId val="155938592"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>20% de la catégorie</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>availability_by_category!$B$77:$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>availability_by_category!$D$77:$D$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C5D5-46C7-8335-F8049FE30E65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="155938112"/>
+        <c:axId val="155938592"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="155938112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4106,8 +5500,8 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -4134,12 +5528,15 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1239484912"/>
+        <c:crossAx val="155938592"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="1239484912"/>
+        <c:axId val="155938592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4165,14 +5562,8 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -4196,9 +5587,9 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="989048816"/>
+        <c:crossAx val="155938112"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -4208,90 +5599,8 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="fr-MA"/>
-              <a:t>Occupation Sports</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
+    <c:legend>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4305,7 +5614,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4320,366 +5629,10 @@
           <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:strRef>
-              <c:f>availability_by_category!$A$77:$A$101</c:f>
-              <c:strCache>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Sports</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Sports</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>availability_by_category!$E$77:$E$101</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>0.1333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.1333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>6.6666666666666666E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6.6666666666666666E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.1333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>6.6666666666666666E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.6666666666666666E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.1333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.1333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>6.6666666666666666E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.6666666666666666E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>6.6666666666666666E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E4D3-43ED-B94B-2AC36E8A4C51}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1240140560"/>
-        <c:axId val="1240133840"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1240140560"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1240133840"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1240133840"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1240140560"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4994,46 +5947,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -6054,7 +6967,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6081,8 +6994,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6183,7 +7096,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -6215,10 +7128,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -6258,23 +7171,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -6379,8 +7291,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6512,20 +7424,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -6539,17 +7450,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -7073,7 +7973,7 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -7100,8 +8000,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7202,7 +8102,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -7234,10 +8134,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -7277,23 +8177,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -7398,8 +8297,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7531,20 +8430,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -7558,17 +8456,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -7589,7 +8476,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -7616,8 +8503,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7718,7 +8605,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -7750,10 +8637,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -7793,23 +8680,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -7914,8 +8800,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8047,20 +8933,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -8074,17 +8959,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -8105,7 +8979,7 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8132,8 +9006,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8234,7 +9108,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -8266,10 +9140,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -8309,23 +9183,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -8430,8 +9303,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8563,20 +9436,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -8590,533 +9462,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -9177,50 +9522,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>475220</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>265148</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>10196</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>171851</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Graphique 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99985D28-D87C-2377-5EC1-31DBBEC378FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>504423</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>579188</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>10195</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>211071</xdr:colOff>
-      <xdr:row>29</xdr:row>
       <xdr:rowOff>123959</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9229,119 +9538,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36728AEE-CB9E-C3EB-7E68-DC665F08F30B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>289775</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>54914</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>604592</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>168677</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Graphique 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44F04284-2A4F-73A2-B043-F818A2872A82}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>129268</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>38553</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>435882</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>19503</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Graphique 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60502292-2464-31ED-16A8-869C4F16D252}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>349251</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>174172</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Graphique 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02C994C0-3723-3482-3A6A-A0AAF4F67C15}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9362,22 +9558,135 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>548821</xdr:colOff>
+      <xdr:colOff>75807</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>7258</xdr:rowOff>
+      <xdr:rowOff>186056</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>258535</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>390624</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>29030</xdr:rowOff>
+      <xdr:rowOff>113460</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Graphique 3">
+        <xdr:cNvPr id="6" name="Graphique 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1EA5F95-9A71-FAB0-4F08-2BE69DFF5A46}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44F04284-2A4F-73A2-B043-F818A2872A82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>594180</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>179614</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>40822</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19957</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Graphique 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4ABFAFA4-8C97-C06A-5E71-F1B4A134F4BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>22678</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>16328</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>340178</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Graphique 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{961519BC-69FD-532F-DB7B-558ABF3BB93F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>18143</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>58964</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>45357</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Graphique 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6AEBE70-A298-EA1A-1FAD-50A5606035C4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9397,23 +9706,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>566965</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>25401</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>607784</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43542</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>276679</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>47172</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>317499</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>18142</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Graphique 4">
+        <xdr:cNvPr id="11" name="Graphique 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C88F8B2-9E32-8FA6-0DDC-30DCC3232E60}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6F4AA40-919C-604F-ED99-E02F7A233808}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15802,10 +16111,11 @@
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" customWidth="1"/>
     <col min="8" max="8" width="25.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15829,10 +16139,10 @@
         <v>297</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -15884,6 +16194,10 @@
       <c r="G3">
         <v>10.975768869559218</v>
       </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H26" si="0">AVERAGE(B:B)</f>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -15905,6 +16219,10 @@
       <c r="G4">
         <v>17.11857333458844</v>
       </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -15926,6 +16244,10 @@
       <c r="G5">
         <v>24.222110586394933</v>
       </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -15947,6 +16269,10 @@
       <c r="G6">
         <v>29.602204753809406</v>
       </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -15968,6 +16294,10 @@
       <c r="G7">
         <v>31.378416847691174</v>
       </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -15989,6 +16319,10 @@
       <c r="G8">
         <v>33.180330056215553</v>
       </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -16010,6 +16344,10 @@
       <c r="G9">
         <v>34.534175153562082</v>
       </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -16031,6 +16369,10 @@
       <c r="G10">
         <v>36.108326306164102</v>
       </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -16052,6 +16394,10 @@
       <c r="G11">
         <v>37.550507384235793</v>
       </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -16067,11 +16413,15 @@
         <v>1994054.0405821139</v>
       </c>
       <c r="E12">
-        <f t="shared" ref="E12:E26" si="0">C12+E11</f>
+        <f t="shared" ref="E12:E26" si="1">C12+E11</f>
         <v>7296.6316782795411</v>
       </c>
       <c r="G12">
         <v>38.896429623705949</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -16088,11 +16438,15 @@
         <v>1997573.847657105</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7694.1540703120136</v>
       </c>
       <c r="G13">
         <v>41.015517228410715</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -16109,11 +16463,15 @@
         <v>1997323.5463978399</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7916.0557577089457</v>
       </c>
       <c r="G14">
         <v>42.198416920731688</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -16130,11 +16488,15 @@
         <v>1998655.3731545701</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8197.1698831822487</v>
       </c>
       <c r="G15">
         <v>43.696962589447722</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -16151,14 +16513,18 @@
         <v>1998311.4553570589</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8402.2720791830725</v>
       </c>
       <c r="G16">
         <v>44.790308599519953</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2041</v>
       </c>
@@ -16172,14 +16538,18 @@
         <v>1977043.6665000001</v>
       </c>
       <c r="E17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8508.5016107680367</v>
       </c>
       <c r="G17">
         <v>45.356590369169048</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2042</v>
       </c>
@@ -16193,14 +16563,18 @@
         <v>1966054.3374892659</v>
       </c>
       <c r="E18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8555.5608745209774</v>
       </c>
       <c r="G18">
         <v>45.60745096093477</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2043</v>
       </c>
@@ -16214,14 +16588,18 @@
         <v>1930456.905631053</v>
       </c>
       <c r="E19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8603.3821207333567</v>
       </c>
       <c r="G19">
         <v>45.862373481329314</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2044</v>
       </c>
@@ -16235,14 +16613,18 @@
         <v>1969599.3847459999</v>
       </c>
       <c r="E20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8623.0834787995755</v>
       </c>
       <c r="G20">
         <v>45.967396253657981</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2045</v>
       </c>
@@ -16256,14 +16638,18 @@
         <v>1849514.1682884321</v>
       </c>
       <c r="E21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8650.5117938380245</v>
       </c>
       <c r="G21">
         <v>46.113609406881231</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2046</v>
       </c>
@@ -16277,14 +16663,18 @@
         <v>1828343.8095022771</v>
       </c>
       <c r="E22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8765.071629800279</v>
       </c>
       <c r="G22">
         <v>46.724297844187653</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2047</v>
       </c>
@@ -16298,14 +16688,18 @@
         <v>1718349.2241290391</v>
       </c>
       <c r="E23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8849.7474732952251</v>
       </c>
       <c r="G23">
         <v>47.175682556003849</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2048</v>
       </c>
@@ -16319,14 +16713,18 @@
         <v>1596391.173170354</v>
       </c>
       <c r="E24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8842.9054066203316</v>
       </c>
       <c r="G24">
         <v>47.139209293184116</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2049</v>
       </c>
@@ -16340,14 +16738,18 @@
         <v>1068476.166736667</v>
       </c>
       <c r="E25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8921.6842520892023</v>
       </c>
       <c r="G25">
         <v>47.55915865526282</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2050</v>
       </c>
@@ -16361,11 +16763,15 @@
         <v>1954903.369697636</v>
       </c>
       <c r="E26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8973.3273540789141</v>
       </c>
       <c r="G26">
         <v>47.834454486361466</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>6.36</v>
       </c>
     </row>
   </sheetData>
@@ -16376,7 +16782,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
@@ -16384,9 +16790,11 @@
     <col min="3" max="3" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -16402,8 +16810,14 @@
       <c r="E1" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -16419,8 +16833,15 @@
       <c r="E2">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" cm="1">
+        <f t="array" ref="F2:F101">(1-E2:E101)*100</f>
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -16436,8 +16857,14 @@
       <c r="E3">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -16453,8 +16880,14 @@
       <c r="E4">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -16470,8 +16903,14 @@
       <c r="E5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -16487,8 +16926,14 @@
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -16504,8 +16949,14 @@
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -16521,8 +16972,14 @@
       <c r="E8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -16538,8 +16995,14 @@
       <c r="E9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -16555,8 +17018,14 @@
       <c r="E10">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -16572,8 +17041,14 @@
       <c r="E11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -16589,8 +17064,14 @@
       <c r="E12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -16606,8 +17087,14 @@
       <c r="E13">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G13">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -16623,8 +17110,14 @@
       <c r="E14">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -16640,8 +17133,14 @@
       <c r="E15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -16657,8 +17156,14 @@
       <c r="E16">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -16674,8 +17179,14 @@
       <c r="E17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -16691,8 +17202,14 @@
       <c r="E18">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G18">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -16708,8 +17225,14 @@
       <c r="E19">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G19">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -16725,8 +17248,14 @@
       <c r="E20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -16742,8 +17271,14 @@
       <c r="E21">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -16759,8 +17294,14 @@
       <c r="E22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -16776,8 +17317,14 @@
       <c r="E23">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G23">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -16793,8 +17340,14 @@
       <c r="E24">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G24">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -16810,8 +17363,14 @@
       <c r="E25">
         <v>0.16666666666666671</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -16827,8 +17386,14 @@
       <c r="E26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -16844,8 +17409,14 @@
       <c r="E27">
         <v>7.6923076923076927E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="G27">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -16861,8 +17432,14 @@
       <c r="E28">
         <v>0.15384615384615391</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28">
+        <v>84.615384615384599</v>
+      </c>
+      <c r="G28">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -16878,8 +17455,14 @@
       <c r="E29">
         <v>0.19230769230769229</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F29">
+        <v>80.769230769230774</v>
+      </c>
+      <c r="G29">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -16895,8 +17478,14 @@
       <c r="E30">
         <v>0.1153846153846154</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F30">
+        <v>88.461538461538453</v>
+      </c>
+      <c r="G30">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -16912,8 +17501,14 @@
       <c r="E31">
         <v>3.8461538461538457E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F31">
+        <v>96.15384615384616</v>
+      </c>
+      <c r="G31">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -16929,8 +17524,14 @@
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -16946,8 +17547,14 @@
       <c r="E33">
         <v>7.6923076923076927E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="G33">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -16963,8 +17570,14 @@
       <c r="E34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -16980,8 +17593,14 @@
       <c r="E35">
         <v>7.6923076923076927E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F35">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="G35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>26</v>
       </c>
@@ -16997,8 +17616,14 @@
       <c r="E36">
         <v>3.8461538461538457E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F36">
+        <v>96.15384615384616</v>
+      </c>
+      <c r="G36">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>26</v>
       </c>
@@ -17014,8 +17639,14 @@
       <c r="E37">
         <v>7.6923076923076927E-2</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F37">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="G37">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>26</v>
       </c>
@@ -17031,8 +17662,14 @@
       <c r="E38">
         <v>0.15384615384615391</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F38">
+        <v>84.615384615384599</v>
+      </c>
+      <c r="G38">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>26</v>
       </c>
@@ -17048,8 +17685,14 @@
       <c r="E39">
         <v>0.1153846153846154</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F39">
+        <v>88.461538461538453</v>
+      </c>
+      <c r="G39">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -17065,8 +17708,14 @@
       <c r="E40">
         <v>0.1153846153846154</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F40">
+        <v>88.461538461538453</v>
+      </c>
+      <c r="G40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -17082,8 +17731,14 @@
       <c r="E41">
         <v>0.19230769230769229</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41">
+        <v>80.769230769230774</v>
+      </c>
+      <c r="G41">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -17099,8 +17754,14 @@
       <c r="E42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42">
+        <v>100</v>
+      </c>
+      <c r="G42">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -17116,8 +17777,14 @@
       <c r="E43">
         <v>7.6923076923076927E-2</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F43">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="G43">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -17133,8 +17800,14 @@
       <c r="E44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F44">
+        <v>100</v>
+      </c>
+      <c r="G44">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -17150,8 +17823,14 @@
       <c r="E45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="G45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -17167,8 +17846,14 @@
       <c r="E46">
         <v>7.6923076923076927E-2</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F46">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="G46">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -17184,8 +17869,14 @@
       <c r="E47">
         <v>0.1153846153846154</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47">
+        <v>88.461538461538453</v>
+      </c>
+      <c r="G47">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -17201,8 +17892,14 @@
       <c r="E48">
         <v>3.8461538461538457E-2</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F48">
+        <v>96.15384615384616</v>
+      </c>
+      <c r="G48">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -17218,8 +17915,14 @@
       <c r="E49">
         <v>0.1153846153846154</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F49">
+        <v>88.461538461538453</v>
+      </c>
+      <c r="G49">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -17235,8 +17938,14 @@
       <c r="E50">
         <v>0.15384615384615391</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F50">
+        <v>84.615384615384599</v>
+      </c>
+      <c r="G50">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -17252,8 +17961,14 @@
       <c r="E51">
         <v>0.15384615384615391</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F51">
+        <v>84.615384615384599</v>
+      </c>
+      <c r="G51">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -17264,13 +17979,19 @@
         <v>3</v>
       </c>
       <c r="D52">
-        <v>5.8000000000000007</v>
+        <v>5.8</v>
       </c>
       <c r="E52">
         <v>0.10344827586206901</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F52">
+        <v>89.65517241379311</v>
+      </c>
+      <c r="G52">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>21</v>
       </c>
@@ -17286,8 +18007,14 @@
       <c r="E53">
         <v>0.17241379310344829</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F53">
+        <v>82.758620689655174</v>
+      </c>
+      <c r="G53">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>21</v>
       </c>
@@ -17303,8 +18030,14 @@
       <c r="E54">
         <v>0.17241379310344829</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F54">
+        <v>82.758620689655174</v>
+      </c>
+      <c r="G54">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>21</v>
       </c>
@@ -17320,8 +18053,14 @@
       <c r="E55">
         <v>0.17241379310344829</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F55">
+        <v>82.758620689655174</v>
+      </c>
+      <c r="G55">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>21</v>
       </c>
@@ -17337,8 +18076,14 @@
       <c r="E56">
         <v>0.17241379310344829</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F56">
+        <v>82.758620689655174</v>
+      </c>
+      <c r="G56">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -17354,8 +18099,14 @@
       <c r="E57">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F57">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G57">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>21</v>
       </c>
@@ -17371,8 +18122,14 @@
       <c r="E58">
         <v>3.4482758620689648E-2</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F58">
+        <v>96.551724137931032</v>
+      </c>
+      <c r="G58">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -17388,8 +18145,14 @@
       <c r="E59">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F59">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G59">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>21</v>
       </c>
@@ -17405,8 +18168,14 @@
       <c r="E60">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F60">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G60">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>21</v>
       </c>
@@ -17422,8 +18191,14 @@
       <c r="E61">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F61">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G61">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -17439,8 +18214,14 @@
       <c r="E62">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F62">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G62">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -17456,8 +18237,14 @@
       <c r="E63">
         <v>3.4482758620689648E-2</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F63">
+        <v>96.551724137931032</v>
+      </c>
+      <c r="G63">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>21</v>
       </c>
@@ -17473,8 +18260,14 @@
       <c r="E64">
         <v>3.4482758620689648E-2</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F64">
+        <v>96.551724137931032</v>
+      </c>
+      <c r="G64">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>21</v>
       </c>
@@ -17490,8 +18283,14 @@
       <c r="E65">
         <v>0.10344827586206901</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F65">
+        <v>89.65517241379311</v>
+      </c>
+      <c r="G65">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>21</v>
       </c>
@@ -17507,8 +18306,14 @@
       <c r="E66">
         <v>0.10344827586206901</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F66">
+        <v>89.65517241379311</v>
+      </c>
+      <c r="G66">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -17524,8 +18329,14 @@
       <c r="E67">
         <v>3.4482758620689648E-2</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F67">
+        <v>96.551724137931032</v>
+      </c>
+      <c r="G67">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -17541,8 +18352,14 @@
       <c r="E68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F68">
+        <v>100</v>
+      </c>
+      <c r="G68">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -17558,8 +18375,14 @@
       <c r="E69">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F69">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G69">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -17575,8 +18398,14 @@
       <c r="E70">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F70">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G70">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -17592,8 +18421,14 @@
       <c r="E71">
         <v>3.4482758620689648E-2</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F71">
+        <v>96.551724137931032</v>
+      </c>
+      <c r="G71">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>21</v>
       </c>
@@ -17609,8 +18444,14 @@
       <c r="E72">
         <v>3.4482758620689648E-2</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F72">
+        <v>96.551724137931032</v>
+      </c>
+      <c r="G72">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -17626,8 +18467,14 @@
       <c r="E73">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F73">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G73">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -17643,8 +18490,14 @@
       <c r="E74">
         <v>0.10344827586206901</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F74">
+        <v>89.65517241379311</v>
+      </c>
+      <c r="G74">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -17660,8 +18513,14 @@
       <c r="E75">
         <v>3.4482758620689648E-2</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F75">
+        <v>96.551724137931032</v>
+      </c>
+      <c r="G75">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -17677,8 +18536,14 @@
       <c r="E76">
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F76">
+        <v>93.103448275862064</v>
+      </c>
+      <c r="G76">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -17694,8 +18559,14 @@
       <c r="E77">
         <v>0.1333333333333333</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F77">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="G77">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -17711,8 +18582,14 @@
       <c r="E78">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F78">
+        <v>80</v>
+      </c>
+      <c r="G78">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -17728,8 +18605,14 @@
       <c r="E79">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F79">
+        <v>80</v>
+      </c>
+      <c r="G79">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -17745,8 +18628,14 @@
       <c r="E80">
         <v>0.1333333333333333</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F80">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="G80">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -17762,8 +18651,14 @@
       <c r="E81">
         <v>0.1333333333333333</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F81">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="G81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -17779,8 +18674,14 @@
       <c r="E82">
         <v>0.1333333333333333</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F82">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="G82">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -17796,8 +18697,14 @@
       <c r="E83">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F83">
+        <v>80</v>
+      </c>
+      <c r="G83">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -17813,8 +18720,14 @@
       <c r="E84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F84">
+        <v>100</v>
+      </c>
+      <c r="G84">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -17830,8 +18743,14 @@
       <c r="E85">
         <v>6.6666666666666666E-2</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F85">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="G85">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>12</v>
       </c>
@@ -17847,8 +18766,14 @@
       <c r="E86">
         <v>6.6666666666666666E-2</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F86">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="G86">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>12</v>
       </c>
@@ -17864,8 +18789,14 @@
       <c r="E87">
         <v>0.1333333333333333</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F87">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="G87">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>12</v>
       </c>
@@ -17881,8 +18812,14 @@
       <c r="E88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F88">
+        <v>100</v>
+      </c>
+      <c r="G88">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>12</v>
       </c>
@@ -17898,8 +18835,14 @@
       <c r="E89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F89">
+        <v>100</v>
+      </c>
+      <c r="G89">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -17915,8 +18858,14 @@
       <c r="E90">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F90">
+        <v>80</v>
+      </c>
+      <c r="G90">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>12</v>
       </c>
@@ -17932,8 +18881,14 @@
       <c r="E91">
         <v>6.6666666666666666E-2</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F91">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="G91">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>12</v>
       </c>
@@ -17949,8 +18904,14 @@
       <c r="E92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>100</v>
+      </c>
+      <c r="G92">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>12</v>
       </c>
@@ -17966,8 +18927,14 @@
       <c r="E93">
         <v>6.6666666666666666E-2</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="G93">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>12</v>
       </c>
@@ -17983,8 +18950,14 @@
       <c r="E94">
         <v>0.1333333333333333</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F94">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="G94">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>12</v>
       </c>
@@ -18000,8 +18973,14 @@
       <c r="E95">
         <v>0.1333333333333333</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F95">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="G95">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -18017,8 +18996,14 @@
       <c r="E96">
         <v>6.6666666666666666E-2</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F96">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="G96">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>12</v>
       </c>
@@ -18034,8 +19019,14 @@
       <c r="E97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F97">
+        <v>100</v>
+      </c>
+      <c r="G97">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>12</v>
       </c>
@@ -18051,8 +19042,14 @@
       <c r="E98">
         <v>6.6666666666666666E-2</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F98">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="G98">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>12</v>
       </c>
@@ -18068,8 +19065,14 @@
       <c r="E99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F99">
+        <v>100</v>
+      </c>
+      <c r="G99">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>12</v>
       </c>
@@ -18085,8 +19088,14 @@
       <c r="E100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F100">
+        <v>100</v>
+      </c>
+      <c r="G100">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>12</v>
       </c>
@@ -18101,6 +19110,12 @@
       </c>
       <c r="E101">
         <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="F101">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="G101">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
